--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE21DF63-296A-426B-AB3D-6ABD143C186A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391270D7-8E21-4F32-ADB5-82EFB8DF767F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3773,80 +3773,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8693D8AD-DBE7-48B9-AC8B-57D2CD9824DF}" name="Programacion" displayName="Programacion" ref="A1:AS272" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
-  <autoFilter ref="A1:AS272" xr:uid="{752E0453-B9B7-4BC5-B073-BF7E49D46DC3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{228A7AB6-0FA6-44EB-A420-47E70BD09372}" name="Programacion" displayName="Programacion" ref="A1:AS272" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
+  <autoFilter ref="A1:AS272" xr:uid="{2C4D1CB6-432A-4AD3-B76A-4D73332AD9F7}"/>
   <tableColumns count="45">
-    <tableColumn id="1" xr3:uid="{9D4539CA-8104-42E5-959E-440F032862FD}" name="CENTRO COSTO" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{D3635AFE-EBF8-40D6-AA30-B47A7A3C737C}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{EAC992C4-02E0-482E-93F7-CEAC09A48149}" name="RUBRO" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{D2D15255-801B-446B-8434-00A360B1B6D3}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{9FA38153-E564-4336-90EB-BC773A283225}" name="META" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{99A3F465-9D65-4A63-912B-8B4E102C9972}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{63837BD0-0A0D-46D2-A583-8AFAB679E275}" name="CLASIFICADOR" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{87893FF0-3D7C-489E-9766-E38C6A625BDE}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{01F6EFB4-86BB-47BA-A05E-0A30788E89D8}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="9" xr3:uid="{8754DF8E-89B5-4F60-B812-054635BD1C37}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{111A959D-95C0-40BA-AD14-C665B1A4260C}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
-    <tableColumn id="10" xr3:uid="{F6AEA512-9229-46A5-82EA-3B0FB3026B6F}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{59722AF5-4662-477B-8D41-2E1B9C20B1C0}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
-    <tableColumn id="11" xr3:uid="{7DBF6587-681A-4F19-90C8-D6C8220101A5}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{D0A113DE-14B8-4264-9352-A19E341D270D}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
-    <tableColumn id="12" xr3:uid="{947151F6-9340-4B89-8B3F-5A1EC9D63310}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{374E9905-892C-4028-9248-55888AE58031}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
-    <tableColumn id="13" xr3:uid="{EEBACB63-323F-4B7A-95FF-025950D8EC21}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{356A1B7C-8EF7-4A74-BD19-7697B34B5516}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
-    <tableColumn id="14" xr3:uid="{5523F0DE-A345-43F2-A9E3-EF27D547E076}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{E44054CA-D9EB-49DE-889D-9637C187370E}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
-    <tableColumn id="15" xr3:uid="{240CE345-23D0-43DD-8DBD-E72588AF78A6}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{7ECC80CD-341C-4209-9040-D71557ED2E7D}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
-    <tableColumn id="16" xr3:uid="{717572B6-8966-4606-9B73-1C0DF2C1FB2D}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{73F54519-B403-4F7D-AB6F-B5E76A156DA8}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
-    <tableColumn id="17" xr3:uid="{A5BA39A2-A67C-40EF-A3C3-6946907CBDCF}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{36725E80-ADF9-42E6-9860-0CEE25214E11}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
-    <tableColumn id="18" xr3:uid="{BFCE7AB8-1190-4BE5-935A-12018073934F}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
-    <tableColumn id="32" xr3:uid="{01D0BE19-B8B1-48B4-AB0A-320388414EE9}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{1C9924A4-FB91-41BB-AC93-B96BB0AC0C0B}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
-    <tableColumn id="33" xr3:uid="{C09D90D9-3FAA-496A-B3ED-D0BA98901D12}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
-    <tableColumn id="20" xr3:uid="{7E3FE7CE-578E-42CC-A1E9-4218E565144A}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{BE9BBDC2-A91A-4955-AD00-81DCF577CAD0}" name="CENTRO COSTO" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{74C07859-449F-463B-9533-85A9E2755996}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{69003492-BA26-44A2-9649-054D739027F4}" name="RUBRO" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{51201693-9443-46BD-8921-35BAEB434D6B}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{AF9A5FC8-E6E9-424F-8AA3-2B3466DA2917}" name="META" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{3413AD06-A613-45BE-BBBB-56A6D468040F}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{6ED5BF03-918F-4785-BBC1-C7B24D243131}" name="CLASIFICADOR" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{B282490F-5AC8-4442-BE75-2FE033238370}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{D1CFB3AF-A2AB-4622-BB8F-6A6B6551E395}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
+    <tableColumn id="9" xr3:uid="{5991471D-EF88-49A9-8FF4-5E0735F881E8}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{871C83AB-47B1-4D49-9A24-C17EEB0F8D32}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
+    <tableColumn id="10" xr3:uid="{D61AD1E5-BBC6-4FD4-9FCE-9FC0B2F120D8}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{E3D11DFD-F9CF-4331-9F2F-CDF3986D6C3A}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
+    <tableColumn id="11" xr3:uid="{B6779818-7F1D-4BFC-BA10-D6A86DEA17E1}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{9A706723-83D5-4AED-865F-EC75884B3A87}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
+    <tableColumn id="12" xr3:uid="{B1F7636B-5EB5-4069-8344-8246E68246EB}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{31053FAB-C2D4-4FDA-BA21-C952EFC5F894}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
+    <tableColumn id="13" xr3:uid="{CA737BEB-04FC-4204-B42A-036A69E7DC8E}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{133171D9-9421-4A35-8BBB-D3419C166FAA}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
+    <tableColumn id="14" xr3:uid="{7D14C866-66E5-4A81-94A2-962A124B0183}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{638906AE-B4FB-4301-98C0-04E5B8929EB3}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
+    <tableColumn id="15" xr3:uid="{D4BECED0-3151-4975-9CDD-AB4434789F1E}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{9FCCAB7F-7CFE-489C-ABA8-3E1290D818A5}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
+    <tableColumn id="16" xr3:uid="{01A33C0D-7A61-43DA-B67B-50C3AFD3BEC4}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{1CFD98C5-20D2-46B8-8315-DC351C0A851B}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
+    <tableColumn id="17" xr3:uid="{A9D9DB39-5244-48A1-8BB0-B1ACF7823A7E}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{2EEECB7A-B341-4ECD-A4BD-47DAA401E1B7}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
+    <tableColumn id="18" xr3:uid="{3818831E-4AF6-4503-8845-6F499E822818}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
+    <tableColumn id="32" xr3:uid="{ABB304AA-CFB2-4F5D-9361-2F40B9014F3D}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{10F9F4C2-4C4D-41C6-BE82-EFE5D16C3397}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
+    <tableColumn id="33" xr3:uid="{70EBFBD0-F859-4E73-B0FE-A0C8DE28C7C0}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="20" xr3:uid="{E9ED7496-648A-4E3E-8B59-3FF258C3078D}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{8BA0E26A-EC04-47CB-86D6-38734BDABC12}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
+    <tableColumn id="37" xr3:uid="{D22C48CF-F410-443F-99E4-1CB97022A3C3}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{7F16A878-D1AC-4456-9057-1C0196E4AF1D}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
+    <tableColumn id="43" xr3:uid="{FB1B8376-D9C4-4960-A2CB-BB38E693B4FE}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{C90FBC42-C4FA-4A9E-BE37-A969F55F7EC7}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
+    <tableColumn id="36" xr3:uid="{3940AA00-6A06-4363-AB49-64687EC1DF93}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{BC3A4B24-6495-40DD-AC00-A04FB4505A25}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
+    <tableColumn id="44" xr3:uid="{FB2B71A2-BC14-4C8F-A88E-0BAE40A8F0F5}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{4D2CB91C-0695-4617-B81E-BC996458910E}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
+    <tableColumn id="39" xr3:uid="{7C5226EE-A674-4201-85FC-ACB43C478DCA}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{AFA61541-084E-4150-A572-BFD489114CFC}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
+    <tableColumn id="45" xr3:uid="{94EA9DD4-A82E-4F03-8F45-272A4ADB9866}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{C003A333-5299-4228-9D42-D3231FD0F5A7}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
+    <tableColumn id="38" xr3:uid="{14E9C3E4-5881-456D-8376-6927BE9DC86E}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{AD9A116D-5EE1-4CE0-9551-9E8C20E0C74D}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
+    <tableColumn id="46" xr3:uid="{DFF830DC-B732-440E-B7AA-AF2D6870BFE7}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{6C1CCB9D-CB05-4973-BBD6-75897218ACEA}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="41" xr3:uid="{7DF3435F-89B1-45BE-A6BF-0AD154B0F0E3}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{3B98CB37-BA41-4DE5-8D47-78E03D68880F}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
+    <tableColumn id="31" xr3:uid="{C50518A5-5FCB-44E0-92A1-DB3F2AA6D8AE}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{166A175D-2FA6-407D-B83F-06B26606BF55}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="40" xr3:uid="{CF34E64C-3066-4396-B0C5-7B000B10CE38}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{A9B92E39-7449-4E54-9299-891C1D77180A}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
+    <tableColumn id="35" xr3:uid="{EF905E24-B58E-49A1-B36C-3F6E3322CA8C}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{B1BA2D53-9093-4950-9CE5-45D4E9663CA4}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
+    <tableColumn id="34" xr3:uid="{5AB18354-910D-417D-92C0-467C67EE0545}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6201,7 +6201,7 @@
         <v>2400</v>
       </c>
       <c r="Y19" s="146">
-        <v>2879.23</v>
+        <v>2400</v>
       </c>
       <c r="Z19" s="145"/>
       <c r="AA19" s="146"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AL19" s="26">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>2879.23</v>
+        <v>2400</v>
       </c>
       <c r="AM19" s="26">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -6259,11 +6259,11 @@
       </c>
       <c r="AR19" s="15">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2879.23</v>
+        <v>2400</v>
       </c>
       <c r="AS19" s="26">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2879.23</v>
+        <v>2400</v>
       </c>
       <c r="AT19" s="94"/>
     </row>
@@ -6416,7 +6416,9 @@
       <c r="X21" s="147">
         <v>2050</v>
       </c>
-      <c r="Y21" s="148"/>
+      <c r="Y21" s="148">
+        <v>1488.55</v>
+      </c>
       <c r="Z21" s="147"/>
       <c r="AA21" s="148"/>
       <c r="AB21" s="147"/>
@@ -6449,7 +6451,7 @@
       </c>
       <c r="AL21" s="149">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>1488.55</v>
       </c>
       <c r="AM21" s="149">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -6473,11 +6475,11 @@
       </c>
       <c r="AR21" s="150">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1488.55</v>
       </c>
       <c r="AS21" s="149">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1488.55</v>
       </c>
       <c r="AT21" s="94"/>
     </row>
@@ -6523,7 +6525,7 @@
         <v>2280</v>
       </c>
       <c r="Y22" s="148">
-        <v>2466.6999999999998</v>
+        <v>2280</v>
       </c>
       <c r="Z22" s="147"/>
       <c r="AA22" s="148"/>
@@ -6557,7 +6559,7 @@
       </c>
       <c r="AL22" s="149">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>2466.6999999999998</v>
+        <v>2280</v>
       </c>
       <c r="AM22" s="149">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -6581,11 +6583,11 @@
       </c>
       <c r="AR22" s="150">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2466.6999999999998</v>
+        <v>2280</v>
       </c>
       <c r="AS22" s="149">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2466.6999999999998</v>
+        <v>2280</v>
       </c>
       <c r="AT22" s="94"/>
     </row>
@@ -8024,7 +8026,9 @@
       <c r="X35" s="147">
         <v>4000</v>
       </c>
-      <c r="Y35" s="148"/>
+      <c r="Y35" s="148">
+        <v>4000</v>
+      </c>
       <c r="Z35" s="147">
         <v>4000</v>
       </c>
@@ -8063,7 +8067,7 @@
       </c>
       <c r="AL35" s="149">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AM35" s="149">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -8087,11 +8091,11 @@
       </c>
       <c r="AR35" s="150">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AS35" s="149">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AT35" s="94"/>
     </row>
@@ -13740,7 +13744,9 @@
       <c r="X86" s="152">
         <v>6000</v>
       </c>
-      <c r="Y86" s="153"/>
+      <c r="Y86" s="153">
+        <v>6000</v>
+      </c>
       <c r="Z86" s="152">
         <v>5000</v>
       </c>
@@ -13779,7 +13785,7 @@
       </c>
       <c r="AL86" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AM86" s="13">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -13803,11 +13809,11 @@
       </c>
       <c r="AR86" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AS86" s="15">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AT86" s="94"/>
     </row>
@@ -13984,7 +13990,9 @@
       <c r="X88" s="152">
         <v>6000</v>
       </c>
-      <c r="Y88" s="153"/>
+      <c r="Y88" s="153">
+        <v>6000</v>
+      </c>
       <c r="Z88" s="152">
         <v>5000</v>
       </c>
@@ -14023,7 +14031,7 @@
       </c>
       <c r="AL88" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AM88" s="13">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -14047,11 +14055,11 @@
       </c>
       <c r="AR88" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AS88" s="15">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AT88" s="94"/>
     </row>
@@ -16292,7 +16300,9 @@
       <c r="X109" s="145">
         <v>7906</v>
       </c>
-      <c r="Y109" s="146"/>
+      <c r="Y109" s="146">
+        <v>7906</v>
+      </c>
       <c r="Z109" s="145"/>
       <c r="AA109" s="146"/>
       <c r="AB109" s="145"/>
@@ -16325,7 +16335,7 @@
       </c>
       <c r="AL109" s="26">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>7906</v>
       </c>
       <c r="AM109" s="26">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -16349,11 +16359,11 @@
       </c>
       <c r="AR109" s="15">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7906</v>
       </c>
       <c r="AS109" s="26">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7906</v>
       </c>
       <c r="AT109" s="94"/>
     </row>
@@ -16720,7 +16730,9 @@
       <c r="X113" s="147">
         <v>5000</v>
       </c>
-      <c r="Y113" s="148"/>
+      <c r="Y113" s="148">
+        <v>5000</v>
+      </c>
       <c r="Z113" s="147">
         <v>5000</v>
       </c>
@@ -16759,7 +16771,7 @@
       </c>
       <c r="AL113" s="149">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AM113" s="149">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -16783,11 +16795,11 @@
       </c>
       <c r="AR113" s="150">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AS113" s="149">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AT113" s="94"/>
     </row>
@@ -17528,7 +17540,9 @@
       <c r="X120" s="41">
         <v>5000</v>
       </c>
-      <c r="Y120" s="144"/>
+      <c r="Y120" s="144">
+        <v>5000</v>
+      </c>
       <c r="Z120" s="41">
         <v>5000</v>
       </c>
@@ -17567,7 +17581,7 @@
       </c>
       <c r="AL120" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AM120" s="13">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -17591,11 +17605,11 @@
       </c>
       <c r="AR120" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AS120" s="15">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AT120" s="94"/>
     </row>
@@ -18884,7 +18898,9 @@
       <c r="X132" s="145">
         <v>4080</v>
       </c>
-      <c r="Y132" s="146"/>
+      <c r="Y132" s="146">
+        <v>4080</v>
+      </c>
       <c r="Z132" s="145">
         <v>4080</v>
       </c>
@@ -18923,7 +18939,7 @@
       </c>
       <c r="AL132" s="26">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>7680</v>
+        <v>11760</v>
       </c>
       <c r="AM132" s="26">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -18947,11 +18963,11 @@
       </c>
       <c r="AR132" s="15">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7680</v>
+        <v>11760</v>
       </c>
       <c r="AS132" s="26">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7680</v>
+        <v>11760</v>
       </c>
       <c r="AT132" s="94"/>
     </row>
@@ -20817,7 +20833,7 @@
         <v>1080</v>
       </c>
       <c r="Y149" s="148">
-        <v>1080</v>
+        <v>399.2</v>
       </c>
       <c r="Z149" s="147"/>
       <c r="AA149" s="148"/>
@@ -20851,7 +20867,7 @@
       </c>
       <c r="AL149" s="149">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>1080</v>
+        <v>399.2</v>
       </c>
       <c r="AM149" s="149">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20875,11 +20891,11 @@
       </c>
       <c r="AR149" s="150">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>1080</v>
+        <v>399.2</v>
       </c>
       <c r="AS149" s="149">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>1080</v>
+        <v>399.2</v>
       </c>
       <c r="AT149" s="94"/>
     </row>
@@ -25036,7 +25052,9 @@
       <c r="X186" s="41">
         <v>5000</v>
       </c>
-      <c r="Y186" s="144"/>
+      <c r="Y186" s="144">
+        <v>5000</v>
+      </c>
       <c r="Z186" s="41">
         <v>5000</v>
       </c>
@@ -25075,7 +25093,7 @@
       </c>
       <c r="AL186" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AM186" s="13">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -25099,11 +25117,11 @@
       </c>
       <c r="AR186" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AS186" s="15">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="AT186" s="94"/>
     </row>
@@ -31037,7 +31055,9 @@
       <c r="X240" s="145">
         <v>6000</v>
       </c>
-      <c r="Y240" s="146"/>
+      <c r="Y240" s="146">
+        <v>6000</v>
+      </c>
       <c r="Z240" s="145">
         <v>6000</v>
       </c>
@@ -31072,7 +31092,7 @@
       </c>
       <c r="AL240" s="26">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AM240" s="26">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -31096,11 +31116,11 @@
       </c>
       <c r="AR240" s="15">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AS240" s="26">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AT240" s="94"/>
     </row>
@@ -34576,13 +34596,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="C191" xr:uid="{3A6CDAB8-4E8C-40BD-9D24-F6F74DC80BA0}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="C191" xr:uid="{79CEA303-1DCD-43F7-87CA-23C7083FD839}">
       <formula1>NOT(ISERROR(SEARCH(("Suministro"),(C191))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C55:C66 C113:C114 C145 C148:C149 C162:C171 C192:C198 C156" xr:uid="{FC400F6E-E07B-48A8-AF2B-C5D4D3280A8A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C55:C66 C113:C114 C145 C148:C149 C162:C171 C192:C198 C156" xr:uid="{903A75AC-B994-4CFA-A162-3C9C60CD0837}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C108:C109 C48 C189 C19:C24 C9 C50:C53 C151 C154:C155" xr:uid="{A777BDEC-FEC7-473F-9811-062B9D504233}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C108:C109 C48 C189 C19:C24 C9 C50:C53 C151 C154:C155" xr:uid="{6B1C355D-5B5A-43D6-9012-A63E861891CE}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83361720-E8A7-4876-8AC5-54D7BFCD54E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9D18EB-1626-4862-A21E-2FD92B27E997}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26885,11 +26885,11 @@
       <c r="W202" s="128"/>
       <c r="X202" s="127"/>
       <c r="Y202" s="128"/>
-      <c r="Z202" s="127">
+      <c r="Z202" s="127"/>
+      <c r="AA202" s="128"/>
+      <c r="AB202" s="127">
         <v>7000</v>
       </c>
-      <c r="AA202" s="128"/>
-      <c r="AB202" s="127"/>
       <c r="AC202" s="128"/>
       <c r="AD202" s="127"/>
       <c r="AE202" s="128"/>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99123BBD-606E-4DF2-B06C-0788BB461F52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E128EC-7AAF-4A83-A518-4930619E603A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4194,21 +4194,21 @@
     <col min="3" max="4" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" style="151" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="152"/>
-    <col min="10" max="10" width="11.42578125" style="151"/>
-    <col min="11" max="11" width="11.42578125" style="152"/>
-    <col min="12" max="12" width="11.42578125" style="151"/>
-    <col min="13" max="13" width="11.42578125" style="152"/>
-    <col min="14" max="14" width="11.42578125" style="151"/>
-    <col min="15" max="15" width="11.42578125" style="152"/>
-    <col min="16" max="16" width="11.42578125" style="151"/>
-    <col min="17" max="17" width="11.42578125" style="152"/>
-    <col min="18" max="18" width="11.42578125" style="151"/>
-    <col min="19" max="19" width="11.42578125" style="152"/>
-    <col min="20" max="20" width="11.42578125" style="151"/>
-    <col min="21" max="21" width="11.42578125" style="152"/>
-    <col min="22" max="22" width="11.42578125" style="151"/>
-    <col min="23" max="23" width="11.42578125" style="152"/>
+    <col min="9" max="9" width="11.42578125" style="152" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="151" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="152" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="151" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="152" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="151" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="152" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="151" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="152" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" style="151" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" style="152" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" style="151" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" style="152" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" style="151" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" style="152" customWidth="1"/>
     <col min="24" max="24" width="11.42578125" style="151"/>
     <col min="25" max="25" width="11.42578125" style="152"/>
     <col min="26" max="26" width="11.42578125" style="151"/>
@@ -9615,11 +9615,11 @@
       <c r="W49" s="126"/>
       <c r="X49" s="125"/>
       <c r="Y49" s="126"/>
-      <c r="Z49" s="125">
+      <c r="Z49" s="125"/>
+      <c r="AA49" s="126"/>
+      <c r="AB49" s="125">
         <v>2000</v>
       </c>
-      <c r="AA49" s="126"/>
-      <c r="AB49" s="125"/>
       <c r="AC49" s="126"/>
       <c r="AD49" s="125"/>
       <c r="AE49" s="126"/>
@@ -20577,8 +20577,12 @@
       <c r="U146" s="124">
         <v>7500</v>
       </c>
-      <c r="V146" s="38"/>
-      <c r="W146" s="124"/>
+      <c r="V146" s="38">
+        <v>7500</v>
+      </c>
+      <c r="W146" s="124">
+        <v>7500</v>
+      </c>
       <c r="X146" s="38"/>
       <c r="Y146" s="124"/>
       <c r="Z146" s="38"/>
@@ -20589,7 +20593,7 @@
       <c r="AE146" s="134"/>
       <c r="AF146" s="11">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>22500</v>
+        <v>30000</v>
       </c>
       <c r="AG146" s="12">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -20609,11 +20613,11 @@
       </c>
       <c r="AK146" s="12">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AL146" s="12">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AM146" s="12">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20633,15 +20637,15 @@
       </c>
       <c r="AQ146" s="13">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AR146" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AS146" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>22500</v>
+        <v>30000</v>
       </c>
       <c r="AT146" s="88"/>
     </row>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E128EC-7AAF-4A83-A518-4930619E603A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14125FEF-153C-4C97-9DBE-CF67D1319817}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="336">
   <si>
     <t>CENTRO COSTO</t>
   </si>
@@ -31037,7 +31037,7 @@
       </c>
       <c r="AT239" s="88"/>
     </row>
-    <row r="240" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:46" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="70" t="s">
         <v>146</v>
       </c>
@@ -31158,29 +31158,26 @@
       <c r="AT240" s="88"/>
     </row>
     <row r="241" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A241" s="161" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="A241" s="70" t="s">
+        <v>146</v>
       </c>
       <c r="B241" s="162" t="s">
         <v>299</v>
       </c>
-      <c r="C241" s="163" t="str">
-        <f>C242</f>
-        <v>LOCACION</v>
-      </c>
-      <c r="D241" s="163" t="s">
+      <c r="C241" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D241" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E241" s="161">
+      <c r="E241" s="67">
         <v>96</v>
       </c>
-      <c r="F241" s="164">
-        <v>23</v>
-      </c>
-      <c r="G241" s="163" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="F241" s="68">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G241" s="59" t="s">
+        <v>57</v>
       </c>
       <c r="H241" s="127"/>
       <c r="I241" s="128"/>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14125FEF-153C-4C97-9DBE-CF67D1319817}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0153BA12-49F1-46AB-BD37-EB57F3FE27FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="339">
   <si>
     <t>CENTRO COSTO</t>
   </si>
@@ -487,9 +487,6 @@
     <t>COFFEE BREAK TALLER 1</t>
   </si>
   <si>
-    <t>SERVICIO DE PUBLICACION/ARTICULO CIENTIFICO</t>
-  </si>
-  <si>
     <t>SERVICIO DE DIAGRAMACION Y PUBLICACION DE ATLAS NACIONAL Y PUNO</t>
   </si>
   <si>
@@ -596,9 +593,6 @@
   </si>
   <si>
     <t>SERVICIO DE SEGUIMIENTO TÉCNICO DE ACTIVIDADES DEL CRF (1/2)</t>
-  </si>
-  <si>
-    <t>MERCH PROYECTO</t>
   </si>
   <si>
     <t>MERCH</t>
@@ -778,9 +772,6 @@
   </si>
   <si>
     <t>VIATICOS (MTA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERVICIO DE COORDINACION Y SISTEMATIZACIÓN DE INFORMACIÓN PARA EL SEB </t>
   </si>
   <si>
     <t>Servicio de asistencia técnica administrativa 3/3</t>
@@ -1054,6 +1045,24 @@
   <si>
     <t>Servicio de coffe break para todos los cursos de capacitación aplicación de imágenes de satélites y otros</t>
   </si>
+  <si>
+    <t>Servicio de Impresion de memoria 1</t>
+  </si>
+  <si>
+    <t>Servicio de Impresion de memoria 2</t>
+  </si>
+  <si>
+    <t>23.27.10 98</t>
+  </si>
+  <si>
+    <t>SERVICIO DE CONDUCCION DE CEREMONIA PROTOCOLAR</t>
+  </si>
+  <si>
+    <t>ALQUILER TRANSPORTE</t>
+  </si>
+  <si>
+    <t>SERVICIO DE ALIMENTACIO COFFE BREAK PUNO</t>
+  </si>
 </sst>
 </file>
 
@@ -1062,7 +1071,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1128,6 +1137,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -1420,7 +1435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1944,6 +1959,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="8" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="13" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4193,6 +4223,7 @@
     <col min="2" max="2" width="57.28515625" customWidth="1"/>
     <col min="3" max="4" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" style="151" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" style="152" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" style="151" customWidth="1"/>
@@ -4209,9 +4240,9 @@
     <col min="21" max="21" width="11.42578125" style="152" customWidth="1"/>
     <col min="22" max="22" width="11.42578125" style="151" customWidth="1"/>
     <col min="23" max="23" width="11.42578125" style="152" customWidth="1"/>
-    <col min="24" max="24" width="11.42578125" style="151"/>
-    <col min="25" max="25" width="11.42578125" style="152"/>
-    <col min="26" max="26" width="11.42578125" style="151"/>
+    <col min="24" max="24" width="11.42578125" style="151" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" style="152" customWidth="1"/>
+    <col min="26" max="26" width="11.42578125" style="151" customWidth="1"/>
     <col min="27" max="27" width="11.42578125" style="152"/>
     <col min="28" max="28" width="11.42578125" style="151"/>
     <col min="29" max="29" width="11.42578125" style="152"/>
@@ -4580,7 +4611,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>47</v>
@@ -4796,7 +4827,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>47</v>
@@ -4904,7 +4935,7 @@
         <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>47</v>
@@ -5123,7 +5154,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D9" s="91" t="s">
         <v>48</v>
@@ -5163,7 +5194,7 @@
       </c>
       <c r="Z9" s="125"/>
       <c r="AA9" s="126">
-        <v>-28.5</v>
+        <v>2353.5</v>
       </c>
       <c r="AB9" s="125"/>
       <c r="AC9" s="126"/>
@@ -5203,7 +5234,7 @@
       </c>
       <c r="AN9" s="14">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>-28.5</v>
+        <v>2353.5</v>
       </c>
       <c r="AO9" s="14">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -5219,11 +5250,11 @@
       </c>
       <c r="AR9" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>230.7</v>
+        <v>2612.6999999999998</v>
       </c>
       <c r="AS9" s="23">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>1370.7</v>
+        <v>3752.7</v>
       </c>
       <c r="AT9" s="88"/>
     </row>
@@ -5882,10 +5913,10 @@
         <v>45</v>
       </c>
       <c r="B16" s="93" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C16" s="90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D16" s="91" t="s">
         <v>48</v>
@@ -5993,7 +6024,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D17" s="91" t="s">
         <v>48</v>
@@ -6098,7 +6129,7 @@
         <v>45</v>
       </c>
       <c r="B18" s="90" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C18" s="90" t="s">
         <v>83</v>
@@ -6206,10 +6237,10 @@
         <v>45</v>
       </c>
       <c r="B19" s="93" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C19" s="90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D19" s="91" t="s">
         <v>48</v>
@@ -6317,7 +6348,7 @@
         <v>50</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D20" s="91" t="s">
         <v>48</v>
@@ -6422,10 +6453,10 @@
         <v>45</v>
       </c>
       <c r="B21" s="93" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D21" s="91" t="s">
         <v>48</v>
@@ -6462,7 +6493,9 @@
         <v>2050</v>
       </c>
       <c r="Z21" s="127"/>
-      <c r="AA21" s="128"/>
+      <c r="AA21" s="128">
+        <v>2119.79</v>
+      </c>
       <c r="AB21" s="127"/>
       <c r="AC21" s="128"/>
       <c r="AD21" s="127"/>
@@ -6501,7 +6534,7 @@
       </c>
       <c r="AN21" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>2119.79</v>
       </c>
       <c r="AO21" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -6517,11 +6550,11 @@
       </c>
       <c r="AR21" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2050</v>
+        <v>4169.79</v>
       </c>
       <c r="AS21" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2050</v>
+        <v>4169.79</v>
       </c>
       <c r="AT21" s="88"/>
     </row>
@@ -6530,10 +6563,10 @@
         <v>45</v>
       </c>
       <c r="B22" s="93" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C22" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D22" s="91" t="s">
         <v>48</v>
@@ -6638,10 +6671,10 @@
         <v>45</v>
       </c>
       <c r="B23" s="93" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D23" s="91" t="s">
         <v>48</v>
@@ -6676,7 +6709,9 @@
       <c r="Z23" s="125">
         <v>1600</v>
       </c>
-      <c r="AA23" s="126"/>
+      <c r="AA23" s="126">
+        <v>1600</v>
+      </c>
       <c r="AB23" s="125"/>
       <c r="AC23" s="126"/>
       <c r="AD23" s="125"/>
@@ -6715,7 +6750,7 @@
       </c>
       <c r="AN23" s="14">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="AO23" s="14">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -6731,11 +6766,11 @@
       </c>
       <c r="AR23" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="AS23" s="23">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="AT23" s="88"/>
     </row>
@@ -6744,10 +6779,10 @@
         <v>45</v>
       </c>
       <c r="B24" s="93" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C24" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D24" s="91" t="s">
         <v>48</v>
@@ -6782,7 +6817,9 @@
       <c r="Z24" s="125">
         <v>1080</v>
       </c>
-      <c r="AA24" s="126"/>
+      <c r="AA24" s="126">
+        <v>1080</v>
+      </c>
       <c r="AB24" s="125"/>
       <c r="AC24" s="126"/>
       <c r="AD24" s="125"/>
@@ -6821,7 +6858,7 @@
       </c>
       <c r="AN24" s="14">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="AO24" s="14">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -6837,11 +6874,11 @@
       </c>
       <c r="AR24" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="AS24" s="23">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="AT24" s="88"/>
     </row>
@@ -6850,10 +6887,10 @@
         <v>45</v>
       </c>
       <c r="B25" s="93" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C25" s="90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D25" s="91" t="s">
         <v>48</v>
@@ -6956,10 +6993,10 @@
         <v>45</v>
       </c>
       <c r="B26" s="93" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C26" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D26" s="91" t="s">
         <v>48</v>
@@ -7236,7 +7273,9 @@
       <c r="Z28" s="38">
         <v>5000</v>
       </c>
-      <c r="AA28" s="124"/>
+      <c r="AA28" s="124">
+        <v>5000</v>
+      </c>
       <c r="AB28" s="38"/>
       <c r="AC28" s="124"/>
       <c r="AD28" s="38"/>
@@ -7275,7 +7314,7 @@
       </c>
       <c r="AN28" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AO28" s="13">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -7291,11 +7330,11 @@
       </c>
       <c r="AR28" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="AS28" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="AT28" s="88"/>
     </row>
@@ -7304,7 +7343,7 @@
         <v>45</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>56</v>
@@ -8370,10 +8409,10 @@
         <v>45</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C38" s="77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D38" s="77" t="s">
         <v>48</v>
@@ -8385,7 +8424,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G38" s="77" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H38" s="125"/>
       <c r="I38" s="126"/>
@@ -9580,10 +9619,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="90" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C49" s="90" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D49" s="91" t="s">
         <v>48</v>
@@ -9617,11 +9656,11 @@
       <c r="Y49" s="126"/>
       <c r="Z49" s="125"/>
       <c r="AA49" s="126"/>
-      <c r="AB49" s="125">
+      <c r="AB49" s="125"/>
+      <c r="AC49" s="126"/>
+      <c r="AD49" s="125">
         <v>2000</v>
       </c>
-      <c r="AC49" s="126"/>
-      <c r="AD49" s="125"/>
       <c r="AE49" s="126"/>
       <c r="AF49" s="23">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -9725,15 +9764,13 @@
       <c r="W50" s="124"/>
       <c r="X50" s="38"/>
       <c r="Y50" s="124"/>
-      <c r="Z50" s="38">
-        <v>880</v>
-      </c>
+      <c r="Z50" s="38"/>
       <c r="AA50" s="124"/>
-      <c r="AB50" s="38"/>
+      <c r="AB50" s="38">
+        <v>1760</v>
+      </c>
       <c r="AC50" s="124"/>
-      <c r="AD50" s="38">
-        <v>880</v>
-      </c>
+      <c r="AD50" s="38"/>
       <c r="AE50" s="124"/>
       <c r="AF50" s="11">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -9798,10 +9835,10 @@
         <v>45</v>
       </c>
       <c r="B51" s="94" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C51" s="90" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D51" s="91" t="s">
         <v>48</v>
@@ -9813,7 +9850,7 @@
         <v>23</v>
       </c>
       <c r="G51" s="96" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H51" s="125"/>
       <c r="I51" s="126"/>
@@ -9906,10 +9943,10 @@
         <v>45</v>
       </c>
       <c r="B52" s="94" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C52" s="90" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D52" s="91" t="s">
         <v>48</v>
@@ -10014,10 +10051,10 @@
         <v>45</v>
       </c>
       <c r="B53" s="107" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C53" s="107" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D53" s="107" t="s">
         <v>48</v>
@@ -10122,10 +10159,10 @@
         <v>45</v>
       </c>
       <c r="B54" s="94" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C54" s="96" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D54" s="91" t="s">
         <v>48</v>
@@ -10228,7 +10265,7 @@
         <v>45</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>79</v>
@@ -10243,7 +10280,7 @@
         <v>2.6</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H55" s="125"/>
       <c r="I55" s="126"/>
@@ -10336,10 +10373,10 @@
         <v>45</v>
       </c>
       <c r="B56" s="90" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C56" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D56" s="91" t="s">
         <v>48</v>
@@ -10369,14 +10406,14 @@
       <c r="U56" s="128"/>
       <c r="V56" s="127"/>
       <c r="W56" s="128"/>
-      <c r="X56" s="131">
-        <v>11000</v>
-      </c>
+      <c r="X56" s="131"/>
       <c r="Y56" s="128"/>
       <c r="Z56" s="131">
+        <v>22000</v>
+      </c>
+      <c r="AA56" s="128">
         <v>11000</v>
       </c>
-      <c r="AA56" s="128"/>
       <c r="AB56" s="131">
         <v>11000</v>
       </c>
@@ -10407,7 +10444,7 @@
       </c>
       <c r="AK56" s="129">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="AL56" s="129">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
@@ -10415,11 +10452,11 @@
       </c>
       <c r="AM56" s="129">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>33000</v>
+        <v>44000</v>
       </c>
       <c r="AN56" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="AO56" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -10435,11 +10472,11 @@
       </c>
       <c r="AR56" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="AS56" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="AT56" s="88"/>
     </row>
@@ -10448,13 +10485,13 @@
         <v>45</v>
       </c>
       <c r="B57" s="90" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C57" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D57" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E57" s="92">
         <v>134</v>
@@ -10562,13 +10599,13 @@
         <v>45</v>
       </c>
       <c r="B58" s="90" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C58" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D58" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E58" s="92">
         <v>134</v>
@@ -10670,13 +10707,13 @@
         <v>45</v>
       </c>
       <c r="B59" s="90" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C59" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D59" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E59" s="92">
         <v>134</v>
@@ -10784,13 +10821,13 @@
         <v>45</v>
       </c>
       <c r="B60" s="90" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C60" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D60" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E60" s="92">
         <v>134</v>
@@ -10817,12 +10854,10 @@
       <c r="U60" s="128"/>
       <c r="V60" s="127"/>
       <c r="W60" s="128"/>
-      <c r="X60" s="131">
-        <v>4500</v>
-      </c>
+      <c r="X60" s="131"/>
       <c r="Y60" s="128"/>
       <c r="Z60" s="131">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="AA60" s="128">
         <v>4500</v>
@@ -10857,7 +10892,7 @@
       </c>
       <c r="AK60" s="129">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="AL60" s="129">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
@@ -10865,7 +10900,7 @@
       </c>
       <c r="AM60" s="129">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>13500</v>
+        <v>18000</v>
       </c>
       <c r="AN60" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -10898,13 +10933,13 @@
         <v>45</v>
       </c>
       <c r="B61" s="90" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C61" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D61" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E61" s="92">
         <v>134</v>
@@ -11006,13 +11041,13 @@
         <v>45</v>
       </c>
       <c r="B62" s="90" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C62" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D62" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E62" s="92">
         <v>134</v>
@@ -11112,13 +11147,13 @@
         <v>45</v>
       </c>
       <c r="B63" s="90" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C63" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D63" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E63" s="92">
         <v>134</v>
@@ -11145,12 +11180,10 @@
       <c r="U63" s="128"/>
       <c r="V63" s="127"/>
       <c r="W63" s="128"/>
-      <c r="X63" s="131">
-        <v>4500</v>
-      </c>
+      <c r="X63" s="131"/>
       <c r="Y63" s="128"/>
       <c r="Z63" s="131">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="AA63" s="128">
         <v>4500</v>
@@ -11185,7 +11218,7 @@
       </c>
       <c r="AK63" s="129">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="AL63" s="129">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
@@ -11193,7 +11226,7 @@
       </c>
       <c r="AM63" s="129">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>13500</v>
+        <v>18000</v>
       </c>
       <c r="AN63" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -11226,13 +11259,13 @@
         <v>45</v>
       </c>
       <c r="B64" s="90" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C64" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D64" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E64" s="92">
         <v>134</v>
@@ -11262,7 +11295,9 @@
       <c r="X64" s="131">
         <v>6500</v>
       </c>
-      <c r="Y64" s="128"/>
+      <c r="Y64" s="128">
+        <v>6500</v>
+      </c>
       <c r="Z64" s="131">
         <v>6500</v>
       </c>
@@ -11303,7 +11338,7 @@
       </c>
       <c r="AL64" s="129">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="AM64" s="129">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -11327,11 +11362,11 @@
       </c>
       <c r="AR64" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>6500</v>
+        <v>13000</v>
       </c>
       <c r="AS64" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>6500</v>
+        <v>13000</v>
       </c>
       <c r="AT64" s="88"/>
     </row>
@@ -11340,13 +11375,13 @@
         <v>45</v>
       </c>
       <c r="B65" s="90" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C65" s="90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D65" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E65" s="92">
         <v>134</v>
@@ -11448,13 +11483,13 @@
         <v>45</v>
       </c>
       <c r="B66" s="93" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C66" s="90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D66" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E66" s="92">
         <v>134</v>
@@ -11485,11 +11520,11 @@
       <c r="Y66" s="128"/>
       <c r="Z66" s="131"/>
       <c r="AA66" s="128"/>
-      <c r="AB66" s="131">
+      <c r="AB66" s="131"/>
+      <c r="AC66" s="128"/>
+      <c r="AD66" s="131">
         <v>2000</v>
       </c>
-      <c r="AC66" s="128"/>
-      <c r="AD66" s="131"/>
       <c r="AE66" s="128"/>
       <c r="AF66" s="129">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -11554,13 +11589,13 @@
         <v>45</v>
       </c>
       <c r="B67" s="93" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C67" s="90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D67" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E67" s="92">
         <v>134</v>
@@ -11591,11 +11626,11 @@
       <c r="Y67" s="128"/>
       <c r="Z67" s="131"/>
       <c r="AA67" s="128"/>
-      <c r="AB67" s="131">
+      <c r="AB67" s="131"/>
+      <c r="AC67" s="128"/>
+      <c r="AD67" s="131">
         <v>1500</v>
       </c>
-      <c r="AC67" s="128"/>
-      <c r="AD67" s="131"/>
       <c r="AE67" s="128"/>
       <c r="AF67" s="129">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -11768,7 +11803,7 @@
         <v>80</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C69" s="19" t="s">
         <v>47</v>
@@ -11882,7 +11917,7 @@
         <v>80</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C70" s="19" t="s">
         <v>47</v>
@@ -11996,7 +12031,7 @@
         <v>80</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C71" s="19" t="s">
         <v>47</v>
@@ -12038,7 +12073,9 @@
       <c r="Z71" s="127">
         <v>400</v>
       </c>
-      <c r="AA71" s="128"/>
+      <c r="AA71" s="128">
+        <v>400</v>
+      </c>
       <c r="AB71" s="127">
         <v>400</v>
       </c>
@@ -12079,7 +12116,7 @@
       </c>
       <c r="AN71" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AO71" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -12095,11 +12132,11 @@
       </c>
       <c r="AR71" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="AS71" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="AT71" s="88"/>
     </row>
@@ -12108,7 +12145,7 @@
         <v>80</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>47</v>
@@ -12150,7 +12187,9 @@
       <c r="Z72" s="127">
         <v>2000</v>
       </c>
-      <c r="AA72" s="128"/>
+      <c r="AA72" s="128">
+        <v>2000</v>
+      </c>
       <c r="AB72" s="127">
         <v>2000</v>
       </c>
@@ -12191,7 +12230,7 @@
       </c>
       <c r="AN72" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AO72" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -12207,11 +12246,11 @@
       </c>
       <c r="AR72" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="AS72" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="AT72" s="88"/>
     </row>
@@ -12220,7 +12259,7 @@
         <v>80</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C73" s="19" t="s">
         <v>47</v>
@@ -12260,7 +12299,9 @@
       <c r="Z73" s="127">
         <v>50</v>
       </c>
-      <c r="AA73" s="128"/>
+      <c r="AA73" s="128">
+        <v>50</v>
+      </c>
       <c r="AB73" s="127">
         <v>50</v>
       </c>
@@ -12301,7 +12342,7 @@
       </c>
       <c r="AN73" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO73" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -12317,11 +12358,11 @@
       </c>
       <c r="AR73" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AS73" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT73" s="88"/>
     </row>
@@ -12330,7 +12371,7 @@
         <v>80</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C74" s="19" t="s">
         <v>47</v>
@@ -12394,7 +12435,9 @@
       <c r="Z74" s="132">
         <v>400</v>
       </c>
-      <c r="AA74" s="133"/>
+      <c r="AA74" s="133">
+        <v>200</v>
+      </c>
       <c r="AB74" s="132">
         <v>400</v>
       </c>
@@ -12437,7 +12480,7 @@
       </c>
       <c r="AN74" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AO74" s="13">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -12453,11 +12496,11 @@
       </c>
       <c r="AR74" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AS74" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AT74" s="88"/>
     </row>
@@ -12466,7 +12509,7 @@
         <v>80</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C75" s="19" t="s">
         <v>47</v>
@@ -12530,7 +12573,9 @@
       <c r="Z75" s="132">
         <v>1200</v>
       </c>
-      <c r="AA75" s="133"/>
+      <c r="AA75" s="133">
+        <v>1200</v>
+      </c>
       <c r="AB75" s="132">
         <v>1200</v>
       </c>
@@ -12573,7 +12618,7 @@
       </c>
       <c r="AN75" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AO75" s="13">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -12589,11 +12634,11 @@
       </c>
       <c r="AR75" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="AS75" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8800</v>
+        <v>10000</v>
       </c>
       <c r="AT75" s="88"/>
     </row>
@@ -12602,7 +12647,7 @@
         <v>80</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C76" s="19" t="s">
         <v>47</v>
@@ -12669,7 +12714,7 @@
         <v>50</v>
       </c>
       <c r="AA76" s="133">
-        <v>-27.7</v>
+        <v>50</v>
       </c>
       <c r="AB76" s="132">
         <v>50</v>
@@ -12713,7 +12758,7 @@
       </c>
       <c r="AN76" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>-27.7</v>
+        <v>50</v>
       </c>
       <c r="AO76" s="13">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -12729,11 +12774,11 @@
       </c>
       <c r="AR76" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8.9000000000000021</v>
+        <v>86.6</v>
       </c>
       <c r="AS76" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>176.09000000000003</v>
+        <v>253.79000000000002</v>
       </c>
       <c r="AT76" s="88"/>
     </row>
@@ -13918,7 +13963,9 @@
       <c r="Z87" s="132">
         <v>4800</v>
       </c>
-      <c r="AA87" s="133"/>
+      <c r="AA87" s="133">
+        <v>580</v>
+      </c>
       <c r="AB87" s="132">
         <v>5600</v>
       </c>
@@ -13961,7 +14008,7 @@
       </c>
       <c r="AN87" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AO87" s="13">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -13977,11 +14024,11 @@
       </c>
       <c r="AR87" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>15000</v>
+        <v>15580</v>
       </c>
       <c r="AS87" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>15000</v>
+        <v>15580</v>
       </c>
       <c r="AT87" s="88"/>
     </row>
@@ -14582,7 +14629,7 @@
         <v>80</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C93" s="19" t="s">
         <v>56</v>
@@ -14628,7 +14675,9 @@
       <c r="Z93" s="132">
         <v>4000</v>
       </c>
-      <c r="AA93" s="133"/>
+      <c r="AA93" s="133">
+        <v>4000</v>
+      </c>
       <c r="AB93" s="132"/>
       <c r="AC93" s="133"/>
       <c r="AD93" s="132"/>
@@ -14667,7 +14716,7 @@
       </c>
       <c r="AN93" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AO93" s="13">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -14683,11 +14732,11 @@
       </c>
       <c r="AR93" s="13">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="AS93" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="AT93" s="88"/>
     </row>
@@ -14696,7 +14745,7 @@
         <v>80</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C94" s="19" t="s">
         <v>56</v>
@@ -14804,7 +14853,7 @@
         <v>80</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C95" s="19" t="s">
         <v>105</v>
@@ -15140,7 +15189,7 @@
         <v>80</v>
       </c>
       <c r="B98" s="87" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C98" s="19" t="s">
         <v>47</v>
@@ -15248,7 +15297,7 @@
         <v>80</v>
       </c>
       <c r="B99" s="87" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C99" s="19" t="s">
         <v>47</v>
@@ -15356,7 +15405,7 @@
         <v>80</v>
       </c>
       <c r="B100" s="87" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C100" s="19" t="s">
         <v>47</v>
@@ -15371,7 +15420,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H100" s="125"/>
       <c r="I100" s="126"/>
@@ -15464,7 +15513,7 @@
         <v>80</v>
       </c>
       <c r="B101" s="87" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C101" s="19" t="s">
         <v>47</v>
@@ -15479,7 +15528,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H101" s="125"/>
       <c r="I101" s="126"/>
@@ -15572,7 +15621,7 @@
         <v>80</v>
       </c>
       <c r="B102" s="87" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C102" s="19" t="s">
         <v>47</v>
@@ -15680,7 +15729,7 @@
         <v>80</v>
       </c>
       <c r="B103" s="87" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C103" s="19" t="s">
         <v>47</v>
@@ -15788,7 +15837,7 @@
         <v>80</v>
       </c>
       <c r="B104" s="87" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C104" s="19" t="s">
         <v>47</v>
@@ -15896,7 +15945,7 @@
         <v>80</v>
       </c>
       <c r="B105" s="87" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C105" s="19" t="s">
         <v>47</v>
@@ -16004,7 +16053,7 @@
         <v>80</v>
       </c>
       <c r="B106" s="87" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C106" s="19" t="s">
         <v>47</v>
@@ -16112,7 +16161,7 @@
         <v>80</v>
       </c>
       <c r="B107" s="87" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C107" s="19" t="s">
         <v>47</v>
@@ -16220,7 +16269,7 @@
         <v>80</v>
       </c>
       <c r="B108" s="87" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C108" s="19" t="s">
         <v>64</v>
@@ -16328,10 +16377,10 @@
         <v>80</v>
       </c>
       <c r="B109" s="97" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D109" s="98" t="s">
         <v>48</v>
@@ -16343,7 +16392,7 @@
         <v>26</v>
       </c>
       <c r="G109" s="98" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H109" s="127"/>
       <c r="I109" s="128"/>
@@ -16436,10 +16485,10 @@
         <v>80</v>
       </c>
       <c r="B110" s="97" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D110" s="98" t="s">
         <v>48</v>
@@ -16451,7 +16500,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="98" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H110" s="125"/>
       <c r="I110" s="126"/>
@@ -16544,7 +16593,7 @@
         <v>80</v>
       </c>
       <c r="B111" s="87" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C111" s="19" t="s">
         <v>64</v>
@@ -16758,7 +16807,7 @@
         <v>80</v>
       </c>
       <c r="B113" s="87" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C113" s="19" t="s">
         <v>64</v>
@@ -16773,7 +16822,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H113" s="127"/>
       <c r="I113" s="128"/>
@@ -16866,10 +16915,10 @@
         <v>80</v>
       </c>
       <c r="B114" s="97" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D114" s="98" t="s">
         <v>48</v>
@@ -16980,13 +17029,13 @@
         <v>80</v>
       </c>
       <c r="B115" s="97" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C115" s="97" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E115" s="20">
         <v>139</v>
@@ -17214,7 +17263,7 @@
         <v>108</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C117" s="26" t="s">
         <v>47</v>
@@ -17334,7 +17383,7 @@
         <v>108</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C118" s="26" t="s">
         <v>47</v>
@@ -17442,7 +17491,7 @@
         <v>108</v>
       </c>
       <c r="B119" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C119" s="26" t="s">
         <v>47</v>
@@ -18802,10 +18851,10 @@
         <v>108</v>
       </c>
       <c r="B131" s="100" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C131" s="100" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D131" s="101" t="s">
         <v>48</v>
@@ -18817,7 +18866,7 @@
         <v>23</v>
       </c>
       <c r="G131" s="101" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H131" s="125"/>
       <c r="I131" s="126"/>
@@ -19080,7 +19129,9 @@
       <c r="Z133" s="125">
         <v>4080</v>
       </c>
-      <c r="AA133" s="126"/>
+      <c r="AA133" s="126">
+        <v>4080</v>
+      </c>
       <c r="AB133" s="125">
         <v>4080</v>
       </c>
@@ -19123,7 +19174,7 @@
       </c>
       <c r="AN133" s="14">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>4080</v>
       </c>
       <c r="AO133" s="14">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -19139,11 +19190,11 @@
       </c>
       <c r="AR133" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>11760</v>
+        <v>15840</v>
       </c>
       <c r="AS133" s="23">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>11760</v>
+        <v>15840</v>
       </c>
       <c r="AT133" s="88"/>
     </row>
@@ -19862,7 +19913,7 @@
         <v>120</v>
       </c>
       <c r="B140" s="168" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C140" s="35" t="s">
         <v>56</v>
@@ -19877,7 +19928,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G140" s="35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H140" s="127"/>
       <c r="I140" s="128"/>
@@ -19970,7 +20021,7 @@
         <v>120</v>
       </c>
       <c r="B141" s="168" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C141" s="35" t="s">
         <v>56</v>
@@ -19985,7 +20036,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G141" s="35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H141" s="127"/>
       <c r="I141" s="128"/>
@@ -20078,10 +20129,10 @@
         <v>120</v>
       </c>
       <c r="B142" s="168" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C142" s="168" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D142" s="157" t="s">
         <v>48</v>
@@ -20116,7 +20167,9 @@
       <c r="Z142" s="127">
         <v>14280</v>
       </c>
-      <c r="AA142" s="128"/>
+      <c r="AA142" s="128">
+        <v>14000</v>
+      </c>
       <c r="AB142" s="127"/>
       <c r="AC142" s="128"/>
       <c r="AD142" s="127"/>
@@ -20155,7 +20208,7 @@
       </c>
       <c r="AN142" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AO142" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -20171,11 +20224,11 @@
       </c>
       <c r="AR142" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AS142" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AT142" s="88"/>
     </row>
@@ -20337,12 +20390,10 @@
       <c r="U144" s="124"/>
       <c r="V144" s="38"/>
       <c r="W144" s="124"/>
-      <c r="X144" s="38">
-        <v>7500</v>
-      </c>
+      <c r="X144" s="38"/>
       <c r="Y144" s="124"/>
       <c r="Z144" s="38">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AA144" s="124">
         <v>7500</v>
@@ -20377,7 +20428,7 @@
       </c>
       <c r="AK144" s="12">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="AL144" s="12">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
@@ -20385,7 +20436,7 @@
       </c>
       <c r="AM144" s="12">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>22500</v>
+        <v>30000</v>
       </c>
       <c r="AN144" s="13">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -20654,10 +20705,10 @@
         <v>120</v>
       </c>
       <c r="B147" s="169" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C147" s="169" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D147" s="169" t="s">
         <v>48</v>
@@ -20768,7 +20819,7 @@
         <v>120</v>
       </c>
       <c r="B148" s="34" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C148" s="35" t="s">
         <v>47</v>
@@ -20876,7 +20927,7 @@
         <v>120</v>
       </c>
       <c r="B149" s="34" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C149" s="35" t="s">
         <v>47</v>
@@ -20984,10 +21035,10 @@
         <v>120</v>
       </c>
       <c r="B150" s="169" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C150" s="169" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D150" s="157" t="s">
         <v>48</v>
@@ -21092,10 +21143,10 @@
         <v>120</v>
       </c>
       <c r="B151" s="169" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C151" s="169" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D151" s="157" t="s">
         <v>48</v>
@@ -21200,7 +21251,7 @@
         <v>120</v>
       </c>
       <c r="B152" s="169" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C152" s="169" t="s">
         <v>73</v>
@@ -21308,10 +21359,10 @@
         <v>120</v>
       </c>
       <c r="B153" s="169" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C153" s="169" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D153" s="157" t="s">
         <v>48</v>
@@ -21418,7 +21469,7 @@
         <v>120</v>
       </c>
       <c r="B154" s="169" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C154" s="169" t="s">
         <v>64</v>
@@ -21526,10 +21577,10 @@
         <v>120</v>
       </c>
       <c r="B155" s="169" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C155" s="169" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D155" s="157" t="s">
         <v>48</v>
@@ -21541,7 +21592,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G155" s="160" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H155" s="125"/>
       <c r="I155" s="126"/>
@@ -21634,10 +21685,10 @@
         <v>120</v>
       </c>
       <c r="B156" s="169" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C156" s="169" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D156" s="157" t="s">
         <v>48</v>
@@ -21742,10 +21793,10 @@
         <v>120</v>
       </c>
       <c r="B157" s="169" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C157" s="169" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D157" s="157" t="s">
         <v>48</v>
@@ -21850,10 +21901,10 @@
         <v>120</v>
       </c>
       <c r="B158" s="168" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C158" s="168" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D158" s="157" t="s">
         <v>48</v>
@@ -21885,11 +21936,11 @@
       <c r="W158" s="128"/>
       <c r="X158" s="127"/>
       <c r="Y158" s="128"/>
-      <c r="Z158" s="127">
+      <c r="Z158" s="127"/>
+      <c r="AA158" s="128"/>
+      <c r="AB158" s="127">
         <v>4000</v>
       </c>
-      <c r="AA158" s="128"/>
-      <c r="AB158" s="127"/>
       <c r="AC158" s="128"/>
       <c r="AD158" s="127"/>
       <c r="AE158" s="128"/>
@@ -21991,11 +22042,11 @@
       <c r="W159" s="124"/>
       <c r="X159" s="38"/>
       <c r="Y159" s="124"/>
-      <c r="Z159" s="38">
+      <c r="Z159" s="38"/>
+      <c r="AA159" s="124"/>
+      <c r="AB159" s="38">
         <v>6000</v>
       </c>
-      <c r="AA159" s="124"/>
-      <c r="AB159" s="38"/>
       <c r="AC159" s="124"/>
       <c r="AD159" s="38"/>
       <c r="AE159" s="124"/>
@@ -22097,11 +22148,11 @@
       <c r="W160" s="124"/>
       <c r="X160" s="38"/>
       <c r="Y160" s="124"/>
-      <c r="Z160" s="38">
+      <c r="Z160" s="38"/>
+      <c r="AA160" s="124"/>
+      <c r="AB160" s="38">
         <v>4000</v>
       </c>
-      <c r="AA160" s="124"/>
-      <c r="AB160" s="38"/>
       <c r="AC160" s="124"/>
       <c r="AD160" s="38"/>
       <c r="AE160" s="134"/>
@@ -22504,13 +22555,13 @@
         <v>120</v>
       </c>
       <c r="B164" s="170" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C164" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D164" s="171" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E164" s="172">
         <v>135</v>
@@ -22616,10 +22667,10 @@
         <v>120</v>
       </c>
       <c r="B165" s="170" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C165" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D165" s="171" t="s">
         <v>48</v>
@@ -22730,13 +22781,13 @@
         <v>120</v>
       </c>
       <c r="B166" s="170" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C166" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D166" s="171" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E166" s="172">
         <v>135</v>
@@ -22844,13 +22895,13 @@
         <v>120</v>
       </c>
       <c r="B167" s="170" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C167" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D167" s="171" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E167" s="172">
         <v>135</v>
@@ -22877,12 +22928,10 @@
       <c r="U167" s="128"/>
       <c r="V167" s="127"/>
       <c r="W167" s="128"/>
-      <c r="X167" s="136">
-        <v>8000</v>
-      </c>
+      <c r="X167" s="136"/>
       <c r="Y167" s="128"/>
       <c r="Z167" s="136">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="AA167" s="128">
         <v>8000</v>
@@ -22917,7 +22966,7 @@
       </c>
       <c r="AK167" s="129">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="AL167" s="129">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
@@ -22925,7 +22974,7 @@
       </c>
       <c r="AM167" s="129">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>24000</v>
+        <v>32000</v>
       </c>
       <c r="AN167" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -22958,10 +23007,10 @@
         <v>120</v>
       </c>
       <c r="B168" s="170" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C168" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D168" s="171" t="s">
         <v>48</v>
@@ -23068,10 +23117,10 @@
         <v>120</v>
       </c>
       <c r="B169" s="170" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C169" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D169" s="171" t="s">
         <v>48</v>
@@ -23178,13 +23227,13 @@
         <v>120</v>
       </c>
       <c r="B170" s="170" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C170" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D170" s="171" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E170" s="172">
         <v>135</v>
@@ -23292,13 +23341,13 @@
         <v>120</v>
       </c>
       <c r="B171" s="170" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C171" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D171" s="171" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E171" s="172">
         <v>135</v>
@@ -23406,13 +23455,13 @@
         <v>120</v>
       </c>
       <c r="B172" s="170" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C172" s="168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D172" s="171" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E172" s="172">
         <v>135</v>
@@ -23762,7 +23811,7 @@
         <v>132</v>
       </c>
       <c r="B175" s="153" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C175" s="40" t="s">
         <v>47</v>
@@ -23906,7 +23955,9 @@
       <c r="Z176" s="127">
         <v>7020</v>
       </c>
-      <c r="AA176" s="128"/>
+      <c r="AA176" s="128">
+        <v>7020</v>
+      </c>
       <c r="AB176" s="127"/>
       <c r="AC176" s="128"/>
       <c r="AD176" s="127"/>
@@ -23945,7 +23996,7 @@
       </c>
       <c r="AN176" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="AO176" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -23961,11 +24012,11 @@
       </c>
       <c r="AR176" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="AS176" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7020</v>
       </c>
       <c r="AT176" s="88"/>
     </row>
@@ -23974,7 +24025,7 @@
         <v>132</v>
       </c>
       <c r="B177" s="143" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C177" s="40" t="s">
         <v>47</v>
@@ -24080,7 +24131,7 @@
         <v>132</v>
       </c>
       <c r="B178" s="153" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C178" s="40" t="s">
         <v>47</v>
@@ -24186,7 +24237,7 @@
         <v>132</v>
       </c>
       <c r="B179" s="153" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C179" s="40" t="s">
         <v>47</v>
@@ -24292,7 +24343,7 @@
         <v>132</v>
       </c>
       <c r="B180" s="153" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C180" s="40" t="s">
         <v>47</v>
@@ -24398,7 +24449,7 @@
         <v>132</v>
       </c>
       <c r="B181" s="153" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C181" s="40" t="s">
         <v>47</v>
@@ -24504,7 +24555,7 @@
         <v>132</v>
       </c>
       <c r="B182" s="153" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C182" s="40" t="s">
         <v>47</v>
@@ -24610,7 +24661,7 @@
         <v>132</v>
       </c>
       <c r="B183" s="153" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C183" s="40" t="s">
         <v>47</v>
@@ -24716,7 +24767,7 @@
         <v>132</v>
       </c>
       <c r="B184" s="153" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C184" s="40" t="s">
         <v>47</v>
@@ -24822,7 +24873,7 @@
         <v>132</v>
       </c>
       <c r="B185" s="153" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C185" s="40" t="s">
         <v>47</v>
@@ -24928,7 +24979,7 @@
         <v>132</v>
       </c>
       <c r="B186" s="153" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C186" s="40" t="s">
         <v>47</v>
@@ -24966,7 +25017,9 @@
       <c r="Z186" s="154">
         <v>400</v>
       </c>
-      <c r="AA186" s="128"/>
+      <c r="AA186" s="128">
+        <v>400</v>
+      </c>
       <c r="AB186" s="127"/>
       <c r="AC186" s="128"/>
       <c r="AD186" s="127"/>
@@ -25005,7 +25058,7 @@
       </c>
       <c r="AN186" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AO186" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -25021,11 +25074,11 @@
       </c>
       <c r="AR186" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AS186" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AT186" s="88"/>
     </row>
@@ -25034,7 +25087,7 @@
         <v>132</v>
       </c>
       <c r="B187" s="153" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C187" s="40" t="s">
         <v>47</v>
@@ -25072,7 +25125,9 @@
       <c r="Z187" s="154">
         <v>1200</v>
       </c>
-      <c r="AA187" s="128"/>
+      <c r="AA187" s="128">
+        <v>1200</v>
+      </c>
       <c r="AB187" s="127"/>
       <c r="AC187" s="128"/>
       <c r="AD187" s="127"/>
@@ -25111,7 +25166,7 @@
       </c>
       <c r="AN187" s="130">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AO187" s="130">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -25127,11 +25182,11 @@
       </c>
       <c r="AR187" s="130">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AS187" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AT187" s="88"/>
     </row>
@@ -25140,7 +25195,7 @@
         <v>132</v>
       </c>
       <c r="B188" s="153" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C188" s="40" t="s">
         <v>47</v>
@@ -25155,7 +25210,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G188" s="42" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H188" s="127"/>
       <c r="I188" s="128"/>
@@ -27070,10 +27125,10 @@
         <v>132</v>
       </c>
       <c r="B204" s="104" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C204" s="103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D204" s="105" t="s">
         <v>48</v>
@@ -27286,10 +27341,10 @@
         <v>132</v>
       </c>
       <c r="B206" s="143" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C206" s="143" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D206" s="105" t="s">
         <v>48</v>
@@ -27301,7 +27356,7 @@
         <v>23</v>
       </c>
       <c r="G206" s="104" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H206" s="127"/>
       <c r="I206" s="128"/>
@@ -27392,13 +27447,13 @@
         <v>132</v>
       </c>
       <c r="B207" s="104" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C207" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D207" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E207" s="108">
         <v>136</v>
@@ -27506,13 +27561,13 @@
         <v>132</v>
       </c>
       <c r="B208" s="104" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C208" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D208" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E208" s="108">
         <v>136</v>
@@ -27620,13 +27675,13 @@
         <v>132</v>
       </c>
       <c r="B209" s="104" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C209" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D209" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E209" s="108">
         <v>136</v>
@@ -27734,13 +27789,13 @@
         <v>132</v>
       </c>
       <c r="B210" s="104" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C210" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D210" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E210" s="108">
         <v>136</v>
@@ -27848,13 +27903,13 @@
         <v>132</v>
       </c>
       <c r="B211" s="104" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C211" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D211" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E211" s="108">
         <v>136</v>
@@ -27962,13 +28017,13 @@
         <v>132</v>
       </c>
       <c r="B212" s="104" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C212" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D212" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E212" s="108">
         <v>136</v>
@@ -28076,13 +28131,13 @@
         <v>132</v>
       </c>
       <c r="B213" s="104" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C213" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D213" s="105" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E213" s="108">
         <v>136</v>
@@ -28628,7 +28683,7 @@
         <v>146</v>
       </c>
       <c r="B218" s="65" t="s">
-        <v>152</v>
+        <v>333</v>
       </c>
       <c r="C218" s="66" t="s">
         <v>56</v>
@@ -28643,7 +28698,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G218" s="69" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="H218" s="125"/>
       <c r="I218" s="126"/>
@@ -28664,7 +28719,7 @@
       <c r="X218" s="125"/>
       <c r="Y218" s="126"/>
       <c r="Z218" s="125">
-        <v>11620.58</v>
+        <v>9800</v>
       </c>
       <c r="AA218" s="126"/>
       <c r="AB218" s="125"/>
@@ -28673,7 +28728,7 @@
       <c r="AE218" s="126"/>
       <c r="AF218" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>11620.58</v>
+        <v>9800</v>
       </c>
       <c r="AG218" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -28701,7 +28756,7 @@
       </c>
       <c r="AM218" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>11620.58</v>
+        <v>9800</v>
       </c>
       <c r="AN218" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -28717,7 +28772,7 @@
       </c>
       <c r="AQ218" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>11620.58</v>
+        <v>9800</v>
       </c>
       <c r="AR218" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -28729,12 +28784,12 @@
       </c>
       <c r="AT218" s="88"/>
     </row>
-    <row r="219" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A219" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B219" s="65" t="s">
-        <v>153</v>
+        <v>334</v>
       </c>
       <c r="C219" s="66" t="s">
         <v>56</v>
@@ -28749,161 +28804,155 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G219" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="H219" s="125"/>
-      <c r="I219" s="126"/>
-      <c r="J219" s="125"/>
-      <c r="K219" s="126"/>
-      <c r="L219" s="125"/>
-      <c r="M219" s="126"/>
-      <c r="N219" s="125"/>
-      <c r="O219" s="126"/>
-      <c r="P219" s="125"/>
-      <c r="Q219" s="126"/>
-      <c r="R219" s="125"/>
-      <c r="S219" s="126"/>
-      <c r="T219" s="125"/>
-      <c r="U219" s="126"/>
-      <c r="V219" s="125"/>
-      <c r="W219" s="126"/>
-      <c r="X219" s="125">
-        <v>13530</v>
-      </c>
-      <c r="Y219" s="126">
-        <v>13530</v>
-      </c>
-      <c r="Z219" s="125">
-        <v>6970</v>
-      </c>
-      <c r="AA219" s="126"/>
-      <c r="AB219" s="125"/>
-      <c r="AC219" s="126"/>
-      <c r="AD219" s="125"/>
-      <c r="AE219" s="126"/>
-      <c r="AF219" s="71">
+        <v>182</v>
+      </c>
+      <c r="H219" s="178"/>
+      <c r="I219" s="179"/>
+      <c r="J219" s="178"/>
+      <c r="K219" s="179"/>
+      <c r="L219" s="178"/>
+      <c r="M219" s="179"/>
+      <c r="N219" s="178"/>
+      <c r="O219" s="179"/>
+      <c r="P219" s="178"/>
+      <c r="Q219" s="179"/>
+      <c r="R219" s="178"/>
+      <c r="S219" s="179"/>
+      <c r="T219" s="178"/>
+      <c r="U219" s="179"/>
+      <c r="V219" s="178"/>
+      <c r="W219" s="179"/>
+      <c r="X219" s="178"/>
+      <c r="Y219" s="179"/>
+      <c r="Z219" s="178">
+        <v>1819</v>
+      </c>
+      <c r="AA219" s="179"/>
+      <c r="AB219" s="178"/>
+      <c r="AC219" s="179"/>
+      <c r="AD219" s="178"/>
+      <c r="AE219" s="179"/>
+      <c r="AF219" s="180">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>20500</v>
-      </c>
-      <c r="AG219" s="63">
+        <v>1819</v>
+      </c>
+      <c r="AG219" s="180">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH219" s="63">
+      <c r="AH219" s="180">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI219" s="63">
+      <c r="AI219" s="180">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ219" s="63">
+      <c r="AJ219" s="180">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK219" s="63">
+      <c r="AK219" s="180">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>13530</v>
-      </c>
-      <c r="AL219" s="63">
+        <v>0</v>
+      </c>
+      <c r="AL219" s="180">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>13530</v>
-      </c>
-      <c r="AM219" s="63">
+        <v>0</v>
+      </c>
+      <c r="AM219" s="180">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>6970</v>
-      </c>
-      <c r="AN219" s="72">
+        <v>1819</v>
+      </c>
+      <c r="AN219" s="181">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO219" s="72">
+      <c r="AO219" s="181">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP219" s="72">
+      <c r="AP219" s="181">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ219" s="72">
+      <c r="AQ219" s="181">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>20500</v>
-      </c>
-      <c r="AR219" s="72">
+        <v>1819</v>
+      </c>
+      <c r="AR219" s="181">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>13530</v>
-      </c>
-      <c r="AS219" s="73">
+        <v>0</v>
+      </c>
+      <c r="AS219" s="180">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>13530</v>
+        <v>0</v>
       </c>
       <c r="AT219" s="88"/>
     </row>
     <row r="220" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="74" t="s">
+      <c r="A220" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B220" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="C220" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="C220" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="D220" s="59" t="s">
+      <c r="D220" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E220" s="60">
+      <c r="E220" s="67">
         <v>34</v>
       </c>
-      <c r="F220" s="61">
+      <c r="F220" s="68">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G220" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="H220" s="145"/>
-      <c r="I220" s="146"/>
-      <c r="J220" s="147">
-        <v>4500</v>
-      </c>
-      <c r="K220" s="146">
-        <v>4500</v>
-      </c>
-      <c r="L220" s="147">
-        <v>10500</v>
-      </c>
-      <c r="M220" s="146">
-        <v>10500</v>
-      </c>
-      <c r="N220" s="147"/>
-      <c r="O220" s="146"/>
-      <c r="P220" s="147"/>
-      <c r="Q220" s="146"/>
-      <c r="R220" s="147"/>
-      <c r="S220" s="146"/>
-      <c r="T220" s="147"/>
-      <c r="U220" s="146"/>
-      <c r="V220" s="147"/>
-      <c r="W220" s="146"/>
-      <c r="X220" s="147"/>
-      <c r="Y220" s="146"/>
-      <c r="Z220" s="147"/>
-      <c r="AA220" s="148"/>
-      <c r="AB220" s="39"/>
-      <c r="AC220" s="135"/>
-      <c r="AD220" s="39"/>
-      <c r="AE220" s="135"/>
-      <c r="AF220" s="62">
+      <c r="G220" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="H220" s="125"/>
+      <c r="I220" s="126"/>
+      <c r="J220" s="125"/>
+      <c r="K220" s="126"/>
+      <c r="L220" s="125"/>
+      <c r="M220" s="126"/>
+      <c r="N220" s="125"/>
+      <c r="O220" s="126"/>
+      <c r="P220" s="125"/>
+      <c r="Q220" s="126"/>
+      <c r="R220" s="125"/>
+      <c r="S220" s="126"/>
+      <c r="T220" s="125"/>
+      <c r="U220" s="126"/>
+      <c r="V220" s="125"/>
+      <c r="W220" s="126"/>
+      <c r="X220" s="125">
+        <v>13530</v>
+      </c>
+      <c r="Y220" s="126">
+        <v>13530</v>
+      </c>
+      <c r="Z220" s="125">
+        <v>6970</v>
+      </c>
+      <c r="AA220" s="126"/>
+      <c r="AB220" s="125"/>
+      <c r="AC220" s="126"/>
+      <c r="AD220" s="125"/>
+      <c r="AE220" s="126"/>
+      <c r="AF220" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>15000</v>
+        <v>20500</v>
       </c>
       <c r="AG220" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AH220" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AI220" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -28915,51 +28964,51 @@
       </c>
       <c r="AK220" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>13530</v>
       </c>
       <c r="AL220" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>13530</v>
       </c>
       <c r="AM220" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AN220" s="64">
+        <v>6970</v>
+      </c>
+      <c r="AN220" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO220" s="64">
+      <c r="AO220" s="72">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>15000</v>
-      </c>
-      <c r="AP220" s="64">
+        <v>0</v>
+      </c>
+      <c r="AP220" s="72">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>15000</v>
-      </c>
-      <c r="AQ220" s="64">
+        <v>0</v>
+      </c>
+      <c r="AQ220" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AR220" s="64">
+        <v>20500</v>
+      </c>
+      <c r="AR220" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS220" s="14">
+        <v>13530</v>
+      </c>
+      <c r="AS220" s="73">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>15000</v>
+        <v>13530</v>
       </c>
       <c r="AT220" s="88"/>
     </row>
-    <row r="221" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:46" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B221" s="65" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C221" s="59" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D221" s="59" t="s">
         <v>148</v>
@@ -28971,18 +29020,22 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G221" s="59" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="H221" s="145"/>
       <c r="I221" s="146"/>
       <c r="J221" s="147">
-        <v>170</v>
+        <v>4500</v>
       </c>
       <c r="K221" s="146">
-        <v>170</v>
-      </c>
-      <c r="L221" s="147"/>
-      <c r="M221" s="146"/>
+        <v>4500</v>
+      </c>
+      <c r="L221" s="147">
+        <v>10500</v>
+      </c>
+      <c r="M221" s="146">
+        <v>10500</v>
+      </c>
       <c r="N221" s="147"/>
       <c r="O221" s="146"/>
       <c r="P221" s="147"/>
@@ -29003,15 +29056,15 @@
       <c r="AE221" s="135"/>
       <c r="AF221" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>170</v>
+        <v>15000</v>
       </c>
       <c r="AG221" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>170</v>
+        <v>15000</v>
       </c>
       <c r="AH221" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>170</v>
+        <v>15000</v>
       </c>
       <c r="AI221" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -29039,11 +29092,11 @@
       </c>
       <c r="AO221" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>170</v>
+        <v>15000</v>
       </c>
       <c r="AP221" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>170</v>
+        <v>15000</v>
       </c>
       <c r="AQ221" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -29055,7 +29108,7 @@
       </c>
       <c r="AS221" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>170</v>
+        <v>15000</v>
       </c>
       <c r="AT221" s="88"/>
     </row>
@@ -29064,7 +29117,7 @@
         <v>146</v>
       </c>
       <c r="B222" s="65" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C222" s="59" t="s">
         <v>47</v>
@@ -29084,10 +29137,10 @@
       <c r="H222" s="145"/>
       <c r="I222" s="146"/>
       <c r="J222" s="147">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K222" s="146">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L222" s="147"/>
       <c r="M222" s="146"/>
@@ -29111,15 +29164,15 @@
       <c r="AE222" s="135"/>
       <c r="AF222" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AG222" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AH222" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AI222" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -29147,11 +29200,11 @@
       </c>
       <c r="AO222" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AP222" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AQ222" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -29163,19 +29216,19 @@
       </c>
       <c r="AS222" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AT222" s="88"/>
     </row>
-    <row r="223" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A223" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B223" s="65" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C223" s="59" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D223" s="59" t="s">
         <v>148</v>
@@ -29187,41 +29240,31 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G223" s="59" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H223" s="145"/>
       <c r="I223" s="146"/>
-      <c r="J223" s="147"/>
-      <c r="K223" s="146"/>
+      <c r="J223" s="147">
+        <v>165</v>
+      </c>
+      <c r="K223" s="146">
+        <v>165</v>
+      </c>
       <c r="L223" s="147"/>
       <c r="M223" s="146"/>
-      <c r="N223" s="147">
-        <v>5848</v>
-      </c>
-      <c r="O223" s="146">
-        <v>5848</v>
-      </c>
-      <c r="P223" s="147">
-        <v>5848</v>
-      </c>
-      <c r="Q223" s="146">
-        <v>5848</v>
-      </c>
-      <c r="R223" s="147">
-        <v>2924</v>
-      </c>
-      <c r="S223" s="146">
-        <v>2924</v>
-      </c>
+      <c r="N223" s="147"/>
+      <c r="O223" s="146"/>
+      <c r="P223" s="147"/>
+      <c r="Q223" s="146"/>
+      <c r="R223" s="147"/>
+      <c r="S223" s="146"/>
       <c r="T223" s="147"/>
       <c r="U223" s="146"/>
       <c r="V223" s="147"/>
       <c r="W223" s="146"/>
       <c r="X223" s="147"/>
       <c r="Y223" s="146"/>
-      <c r="Z223" s="147">
-        <v>0.39</v>
-      </c>
+      <c r="Z223" s="147"/>
       <c r="AA223" s="148"/>
       <c r="AB223" s="39"/>
       <c r="AC223" s="135"/>
@@ -29229,23 +29272,23 @@
       <c r="AE223" s="135"/>
       <c r="AF223" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>14620.39</v>
+        <v>165</v>
       </c>
       <c r="AG223" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AH223" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AI223" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>14620</v>
+        <v>0</v>
       </c>
       <c r="AJ223" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>14620</v>
+        <v>0</v>
       </c>
       <c r="AK223" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
@@ -29257,7 +29300,7 @@
       </c>
       <c r="AM223" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="AN223" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -29265,15 +29308,15 @@
       </c>
       <c r="AO223" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>14620</v>
+        <v>165</v>
       </c>
       <c r="AP223" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>14620</v>
+        <v>165</v>
       </c>
       <c r="AQ223" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="AR223" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -29281,73 +29324,71 @@
       </c>
       <c r="AS223" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>14620</v>
+        <v>165</v>
       </c>
       <c r="AT223" s="88"/>
     </row>
     <row r="224" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A224" s="70" t="s">
+      <c r="A224" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B224" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="C224" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="C224" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="D224" s="69" t="s">
+      <c r="D224" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E224" s="67">
+      <c r="E224" s="60">
         <v>34</v>
       </c>
-      <c r="F224" s="68">
+      <c r="F224" s="61">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G224" s="69" t="s">
+      <c r="G224" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H224" s="125"/>
-      <c r="I224" s="126"/>
-      <c r="J224" s="125"/>
-      <c r="K224" s="126"/>
-      <c r="L224" s="125"/>
-      <c r="M224" s="126"/>
-      <c r="N224" s="125"/>
-      <c r="O224" s="126"/>
-      <c r="P224" s="125"/>
-      <c r="Q224" s="126"/>
-      <c r="R224" s="125"/>
-      <c r="S224" s="126"/>
-      <c r="T224" s="125">
-        <v>6000</v>
-      </c>
-      <c r="U224" s="126">
-        <v>6000</v>
-      </c>
-      <c r="V224" s="125">
-        <v>6000</v>
-      </c>
-      <c r="W224" s="126">
-        <v>6000</v>
-      </c>
-      <c r="X224" s="125">
-        <v>6000</v>
-      </c>
-      <c r="Y224" s="126">
-        <v>6000</v>
-      </c>
-      <c r="Z224" s="125">
-        <v>12000</v>
-      </c>
-      <c r="AA224" s="126"/>
-      <c r="AB224" s="125"/>
-      <c r="AC224" s="126"/>
-      <c r="AD224" s="125"/>
-      <c r="AE224" s="126"/>
-      <c r="AF224" s="71">
+      <c r="H224" s="145"/>
+      <c r="I224" s="146"/>
+      <c r="J224" s="147"/>
+      <c r="K224" s="146"/>
+      <c r="L224" s="147"/>
+      <c r="M224" s="146"/>
+      <c r="N224" s="147">
+        <v>5848</v>
+      </c>
+      <c r="O224" s="146">
+        <v>5848</v>
+      </c>
+      <c r="P224" s="147">
+        <v>5848</v>
+      </c>
+      <c r="Q224" s="146">
+        <v>5848</v>
+      </c>
+      <c r="R224" s="147">
+        <v>2924</v>
+      </c>
+      <c r="S224" s="146">
+        <v>2924</v>
+      </c>
+      <c r="T224" s="147"/>
+      <c r="U224" s="146"/>
+      <c r="V224" s="147"/>
+      <c r="W224" s="146"/>
+      <c r="X224" s="147"/>
+      <c r="Y224" s="146"/>
+      <c r="Z224" s="147"/>
+      <c r="AA224" s="148"/>
+      <c r="AB224" s="39"/>
+      <c r="AC224" s="135"/>
+      <c r="AD224" s="39"/>
+      <c r="AE224" s="135"/>
+      <c r="AF224" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>30000</v>
+        <v>14620</v>
       </c>
       <c r="AG224" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -29359,71 +29400,71 @@
       </c>
       <c r="AI224" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
+        <v>14620</v>
       </c>
       <c r="AJ224" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
+        <v>14620</v>
       </c>
       <c r="AK224" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="AL224" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="AM224" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>12000</v>
-      </c>
-      <c r="AN224" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN224" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO224" s="72">
+      <c r="AO224" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AP224" s="72">
+        <v>14620</v>
+      </c>
+      <c r="AP224" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AQ224" s="72">
+        <v>14620</v>
+      </c>
+      <c r="AQ224" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>30000</v>
-      </c>
-      <c r="AR224" s="72">
+        <v>0</v>
+      </c>
+      <c r="AR224" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>18000</v>
-      </c>
-      <c r="AS224" s="73">
+        <v>0</v>
+      </c>
+      <c r="AS224" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>18000</v>
+        <v>14620</v>
       </c>
       <c r="AT224" s="88"/>
     </row>
-    <row r="225" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A225" s="74" t="s">
+    <row r="225" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+      <c r="A225" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B225" s="65" t="s">
-        <v>163</v>
-      </c>
-      <c r="C225" s="59" t="s">
-        <v>164</v>
-      </c>
-      <c r="D225" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="C225" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D225" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E225" s="60">
-        <v>95</v>
-      </c>
-      <c r="F225" s="61">
+      <c r="E225" s="67">
+        <v>34</v>
+      </c>
+      <c r="F225" s="68">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G225" s="59" t="s">
-        <v>165</v>
+      <c r="G225" s="69" t="s">
+        <v>57</v>
       </c>
       <c r="H225" s="125"/>
       <c r="I225" s="126"/>
@@ -29437,75 +29478,89 @@
       <c r="Q225" s="126"/>
       <c r="R225" s="125"/>
       <c r="S225" s="126"/>
-      <c r="T225" s="125"/>
-      <c r="U225" s="126"/>
-      <c r="V225" s="125"/>
-      <c r="W225" s="126"/>
-      <c r="X225" s="125"/>
-      <c r="Y225" s="126"/>
+      <c r="T225" s="125">
+        <v>6000</v>
+      </c>
+      <c r="U225" s="126">
+        <v>6000</v>
+      </c>
+      <c r="V225" s="125">
+        <v>6000</v>
+      </c>
+      <c r="W225" s="126">
+        <v>6000</v>
+      </c>
+      <c r="X225" s="125">
+        <v>6000</v>
+      </c>
+      <c r="Y225" s="126">
+        <v>6000</v>
+      </c>
       <c r="Z225" s="125">
-        <v>700</v>
-      </c>
-      <c r="AA225" s="126"/>
+        <v>12000</v>
+      </c>
+      <c r="AA225" s="126">
+        <v>6000</v>
+      </c>
       <c r="AB225" s="125"/>
       <c r="AC225" s="126"/>
       <c r="AD225" s="125"/>
       <c r="AE225" s="126"/>
-      <c r="AF225" s="23">
+      <c r="AF225" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>700</v>
-      </c>
-      <c r="AG225" s="23">
+        <v>30000</v>
+      </c>
+      <c r="AG225" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH225" s="23">
+      <c r="AH225" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI225" s="23">
+      <c r="AI225" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ225" s="23">
+      <c r="AJ225" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK225" s="23">
+      <c r="AK225" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AL225" s="23">
+        <v>18000</v>
+      </c>
+      <c r="AL225" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AM225" s="23">
+        <v>18000</v>
+      </c>
+      <c r="AM225" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>700</v>
-      </c>
-      <c r="AN225" s="14">
+        <v>12000</v>
+      </c>
+      <c r="AN225" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AO225" s="14">
+        <v>6000</v>
+      </c>
+      <c r="AO225" s="72">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP225" s="14">
+      <c r="AP225" s="72">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ225" s="14">
+      <c r="AQ225" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>700</v>
-      </c>
-      <c r="AR225" s="14">
+        <v>30000</v>
+      </c>
+      <c r="AR225" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS225" s="23">
+        <v>24000</v>
+      </c>
+      <c r="AS225" s="73">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="AT225" s="88"/>
     </row>
@@ -29514,7 +29569,7 @@
         <v>146</v>
       </c>
       <c r="B226" s="65" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C226" s="66" t="s">
         <v>47</v>
@@ -29622,7 +29677,7 @@
         <v>146</v>
       </c>
       <c r="B227" s="65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C227" s="66" t="s">
         <v>47</v>
@@ -29730,7 +29785,7 @@
         <v>146</v>
       </c>
       <c r="B228" s="65" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C228" s="66" t="s">
         <v>47</v>
@@ -29766,7 +29821,7 @@
       <c r="X228" s="125"/>
       <c r="Y228" s="126"/>
       <c r="Z228" s="125">
-        <v>7100.93</v>
+        <v>7800.93</v>
       </c>
       <c r="AA228" s="126"/>
       <c r="AB228" s="125"/>
@@ -29775,7 +29830,7 @@
       <c r="AE228" s="126"/>
       <c r="AF228" s="23">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7100.93</v>
+        <v>7800.93</v>
       </c>
       <c r="AG228" s="23">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -29803,7 +29858,7 @@
       </c>
       <c r="AM228" s="23">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7100.93</v>
+        <v>7800.93</v>
       </c>
       <c r="AN228" s="14">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -29819,7 +29874,7 @@
       </c>
       <c r="AQ228" s="14">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7100.93</v>
+        <v>7800.93</v>
       </c>
       <c r="AR228" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -29836,7 +29891,7 @@
         <v>146</v>
       </c>
       <c r="B229" s="65" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C229" s="66" t="s">
         <v>47</v>
@@ -29942,7 +29997,7 @@
         <v>146</v>
       </c>
       <c r="B230" s="65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C230" s="66" t="s">
         <v>73</v>
@@ -30050,7 +30105,7 @@
         <v>146</v>
       </c>
       <c r="B231" s="65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C231" s="59" t="s">
         <v>56</v>
@@ -30158,7 +30213,7 @@
         <v>146</v>
       </c>
       <c r="B232" s="65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C232" s="66" t="s">
         <v>56</v>
@@ -30270,10 +30325,10 @@
         <v>146</v>
       </c>
       <c r="B233" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="C233" s="59" t="s">
         <v>163</v>
-      </c>
-      <c r="C233" s="59" t="s">
-        <v>164</v>
       </c>
       <c r="D233" s="59" t="s">
         <v>148</v>
@@ -30285,7 +30340,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G233" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H233" s="145"/>
       <c r="I233" s="146"/>
@@ -30378,7 +30433,7 @@
         <v>146</v>
       </c>
       <c r="B234" s="65" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C234" s="59" t="s">
         <v>73</v>
@@ -30486,7 +30541,7 @@
         <v>146</v>
       </c>
       <c r="B235" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C235" s="59" t="s">
         <v>56</v>
@@ -30598,10 +30653,10 @@
         <v>146</v>
       </c>
       <c r="B236" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="C236" s="59" t="s">
         <v>168</v>
-      </c>
-      <c r="C236" s="59" t="s">
-        <v>169</v>
       </c>
       <c r="D236" s="59" t="s">
         <v>148</v>
@@ -30613,7 +30668,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G236" s="59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H236" s="125"/>
       <c r="I236" s="126"/>
@@ -30706,7 +30761,7 @@
         <v>146</v>
       </c>
       <c r="B237" s="65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C237" s="59" t="s">
         <v>56</v>
@@ -30818,7 +30873,7 @@
         <v>146</v>
       </c>
       <c r="B238" s="65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C238" s="59" t="s">
         <v>56</v>
@@ -30930,7 +30985,7 @@
         <v>146</v>
       </c>
       <c r="B239" s="65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C239" s="59" t="s">
         <v>56</v>
@@ -31042,7 +31097,7 @@
         <v>146</v>
       </c>
       <c r="B240" s="65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C240" s="66" t="s">
         <v>56</v>
@@ -31162,7 +31217,7 @@
         <v>146</v>
       </c>
       <c r="B241" s="162" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C241" s="66" t="s">
         <v>56</v>
@@ -31272,7 +31327,7 @@
         <v>146</v>
       </c>
       <c r="B242" s="65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C242" s="66" t="s">
         <v>56</v>
@@ -31319,9 +31374,7 @@
       <c r="Y242" s="126">
         <v>5000</v>
       </c>
-      <c r="Z242" s="125">
-        <v>3800</v>
-      </c>
+      <c r="Z242" s="125"/>
       <c r="AA242" s="126"/>
       <c r="AB242" s="125"/>
       <c r="AC242" s="126"/>
@@ -31329,7 +31382,7 @@
       <c r="AE242" s="126"/>
       <c r="AF242" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>18800</v>
+        <v>15000</v>
       </c>
       <c r="AG242" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -31357,7 +31410,7 @@
       </c>
       <c r="AM242" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="AN242" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -31373,7 +31426,7 @@
       </c>
       <c r="AQ242" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>13800</v>
+        <v>10000</v>
       </c>
       <c r="AR242" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -31385,15 +31438,15 @@
       </c>
       <c r="AT242" s="88"/>
     </row>
-    <row r="243" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A243" s="161" t="s">
         <v>146</v>
       </c>
       <c r="B243" s="162" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="C243" s="163" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D243" s="163" t="s">
         <v>148</v>
@@ -31405,7 +31458,7 @@
         <v>23</v>
       </c>
       <c r="G243" s="163" t="s">
-        <v>57</v>
+        <v>335</v>
       </c>
       <c r="H243" s="125"/>
       <c r="I243" s="126"/>
@@ -31425,17 +31478,17 @@
       <c r="W243" s="126"/>
       <c r="X243" s="125"/>
       <c r="Y243" s="126"/>
-      <c r="Z243" s="125">
-        <v>6000</v>
-      </c>
+      <c r="Z243" s="125"/>
       <c r="AA243" s="126"/>
-      <c r="AB243" s="125"/>
+      <c r="AB243" s="125">
+        <v>3000</v>
+      </c>
       <c r="AC243" s="126"/>
       <c r="AD243" s="125"/>
       <c r="AE243" s="126"/>
       <c r="AF243" s="23">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AG243" s="23">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -31463,7 +31516,7 @@
       </c>
       <c r="AM243" s="23">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AN243" s="14">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -31479,7 +31532,7 @@
       </c>
       <c r="AQ243" s="14">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AR243" s="14">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -31491,577 +31544,569 @@
       </c>
       <c r="AT243" s="88"/>
     </row>
-    <row r="244" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A244" s="74" t="s">
+    <row r="244" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A244" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="B244" s="65" t="s">
-        <v>175</v>
-      </c>
-      <c r="C244" s="59" t="s">
+      <c r="B244" s="76" t="s">
+        <v>337</v>
+      </c>
+      <c r="C244" s="103" t="s">
+        <v>234</v>
+      </c>
+      <c r="D244" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="E244" s="161">
+        <v>96</v>
+      </c>
+      <c r="F244" s="164">
+        <v>23</v>
+      </c>
+      <c r="G244" s="177"/>
+      <c r="H244" s="178"/>
+      <c r="I244" s="179"/>
+      <c r="J244" s="178"/>
+      <c r="K244" s="179"/>
+      <c r="L244" s="178"/>
+      <c r="M244" s="179"/>
+      <c r="N244" s="178"/>
+      <c r="O244" s="179"/>
+      <c r="P244" s="178"/>
+      <c r="Q244" s="179"/>
+      <c r="R244" s="178"/>
+      <c r="S244" s="179"/>
+      <c r="T244" s="178"/>
+      <c r="U244" s="179"/>
+      <c r="V244" s="178"/>
+      <c r="W244" s="179"/>
+      <c r="X244" s="178"/>
+      <c r="Y244" s="179"/>
+      <c r="Z244" s="178"/>
+      <c r="AA244" s="179"/>
+      <c r="AB244" s="178">
+        <v>1473</v>
+      </c>
+      <c r="AC244" s="179"/>
+      <c r="AD244" s="178"/>
+      <c r="AE244" s="179"/>
+      <c r="AF244" s="180">
+        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>1473</v>
+      </c>
+      <c r="AG244" s="180">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AH244" s="180">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AI244" s="180">
+        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AJ244" s="180">
+        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AK244" s="180">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AL244" s="180">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AM244" s="180">
+        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>1473</v>
+      </c>
+      <c r="AN244" s="181">
+        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AO244" s="181">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AP244" s="181">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AQ244" s="181">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>1473</v>
+      </c>
+      <c r="AR244" s="181">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AS244" s="180">
+        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AT244" s="88"/>
+    </row>
+    <row r="245" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A245" s="161" t="s">
+        <v>146</v>
+      </c>
+      <c r="B245" s="76" t="s">
+        <v>338</v>
+      </c>
+      <c r="C245" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="D245" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="E245" s="161">
+        <v>96</v>
+      </c>
+      <c r="F245" s="164">
+        <v>23</v>
+      </c>
+      <c r="G245" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="H245" s="178"/>
+      <c r="I245" s="179"/>
+      <c r="J245" s="178"/>
+      <c r="K245" s="179"/>
+      <c r="L245" s="178"/>
+      <c r="M245" s="179"/>
+      <c r="N245" s="178"/>
+      <c r="O245" s="179"/>
+      <c r="P245" s="178"/>
+      <c r="Q245" s="179"/>
+      <c r="R245" s="178"/>
+      <c r="S245" s="179"/>
+      <c r="T245" s="178"/>
+      <c r="U245" s="179"/>
+      <c r="V245" s="178"/>
+      <c r="W245" s="179"/>
+      <c r="X245" s="178"/>
+      <c r="Y245" s="179"/>
+      <c r="Z245" s="178"/>
+      <c r="AA245" s="179"/>
+      <c r="AB245" s="178">
+        <v>7300</v>
+      </c>
+      <c r="AC245" s="179"/>
+      <c r="AD245" s="178"/>
+      <c r="AE245" s="179"/>
+      <c r="AF245" s="180">
+        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>7300</v>
+      </c>
+      <c r="AG245" s="180">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AH245" s="180">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AI245" s="180">
+        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AJ245" s="180">
+        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AK245" s="180">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AL245" s="180">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AM245" s="180">
+        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>7300</v>
+      </c>
+      <c r="AN245" s="181">
+        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AO245" s="181">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AP245" s="181">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AQ245" s="181">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>7300</v>
+      </c>
+      <c r="AR245" s="181">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AS245" s="180">
+        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AT245" s="88"/>
+    </row>
+    <row r="246" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+      <c r="A246" s="74" t="s">
+        <v>146</v>
+      </c>
+      <c r="B246" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="C246" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="D244" s="59" t="s">
+      <c r="D246" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E244" s="60">
+      <c r="E246" s="60">
         <v>96</v>
       </c>
-      <c r="F244" s="61">
+      <c r="F246" s="61">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G244" s="59" t="s">
+      <c r="G246" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H244" s="145">
+      <c r="H246" s="145">
         <v>8774</v>
       </c>
-      <c r="I244" s="146">
+      <c r="I246" s="146">
         <v>8774</v>
       </c>
-      <c r="J244" s="147"/>
-      <c r="K244" s="146"/>
-      <c r="L244" s="147">
+      <c r="J246" s="147"/>
+      <c r="K246" s="146"/>
+      <c r="L246" s="147">
         <v>8774</v>
       </c>
-      <c r="M244" s="146">
+      <c r="M246" s="146">
         <v>8774</v>
       </c>
-      <c r="N244" s="147"/>
-      <c r="O244" s="146"/>
-      <c r="P244" s="147"/>
-      <c r="Q244" s="146"/>
-      <c r="R244" s="147"/>
-      <c r="S244" s="146"/>
-      <c r="T244" s="147"/>
-      <c r="U244" s="146"/>
-      <c r="V244" s="147"/>
-      <c r="W244" s="146"/>
-      <c r="X244" s="147"/>
-      <c r="Y244" s="146"/>
-      <c r="Z244" s="147"/>
-      <c r="AA244" s="148"/>
-      <c r="AB244" s="39"/>
-      <c r="AC244" s="135"/>
-      <c r="AD244" s="39"/>
-      <c r="AE244" s="135"/>
-      <c r="AF244" s="62">
+      <c r="N246" s="147"/>
+      <c r="O246" s="146"/>
+      <c r="P246" s="147"/>
+      <c r="Q246" s="146"/>
+      <c r="R246" s="147"/>
+      <c r="S246" s="146"/>
+      <c r="T246" s="147"/>
+      <c r="U246" s="146"/>
+      <c r="V246" s="147"/>
+      <c r="W246" s="146"/>
+      <c r="X246" s="147"/>
+      <c r="Y246" s="146"/>
+      <c r="Z246" s="147"/>
+      <c r="AA246" s="148"/>
+      <c r="AB246" s="39"/>
+      <c r="AC246" s="135"/>
+      <c r="AD246" s="39"/>
+      <c r="AE246" s="135"/>
+      <c r="AF246" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>17548</v>
       </c>
-      <c r="AG244" s="63">
+      <c r="AG246" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>17548</v>
       </c>
-      <c r="AH244" s="63">
+      <c r="AH246" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>17548</v>
       </c>
-      <c r="AI244" s="63">
+      <c r="AI246" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ244" s="63">
+      <c r="AJ246" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK244" s="63">
+      <c r="AK246" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL244" s="63">
+      <c r="AL246" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM244" s="63">
+      <c r="AM246" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN244" s="64">
+      <c r="AN246" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO244" s="64">
+      <c r="AO246" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>17548</v>
       </c>
-      <c r="AP244" s="64">
+      <c r="AP246" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>17548</v>
       </c>
-      <c r="AQ244" s="64">
+      <c r="AQ246" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AR244" s="64">
+      <c r="AR246" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS244" s="14">
+      <c r="AS246" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>17548</v>
       </c>
-      <c r="AT244" s="88"/>
+      <c r="AT246" s="88"/>
     </row>
-    <row r="245" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A245" s="74" t="s">
+    <row r="247" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+      <c r="A247" s="74" t="s">
         <v>146</v>
       </c>
-      <c r="B245" s="65" t="s">
-        <v>176</v>
-      </c>
-      <c r="C245" s="59" t="s">
+      <c r="B247" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="C247" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="D245" s="59" t="s">
+      <c r="D247" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E245" s="60">
+      <c r="E247" s="60">
         <v>96</v>
       </c>
-      <c r="F245" s="61">
+      <c r="F247" s="61">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G245" s="59" t="s">
+      <c r="G247" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H245" s="145"/>
-      <c r="I245" s="146"/>
-      <c r="J245" s="147"/>
-      <c r="K245" s="146"/>
-      <c r="L245" s="147">
+      <c r="H247" s="145"/>
+      <c r="I247" s="146"/>
+      <c r="J247" s="147"/>
+      <c r="K247" s="146"/>
+      <c r="L247" s="147">
         <v>8520</v>
       </c>
-      <c r="M245" s="146">
+      <c r="M247" s="146">
         <v>8520</v>
       </c>
-      <c r="N245" s="147">
+      <c r="N247" s="147">
         <v>5680</v>
       </c>
-      <c r="O245" s="146">
+      <c r="O247" s="146">
         <v>5680</v>
       </c>
-      <c r="P245" s="147"/>
-      <c r="Q245" s="146"/>
-      <c r="R245" s="147"/>
-      <c r="S245" s="146"/>
-      <c r="T245" s="147"/>
-      <c r="U245" s="146"/>
-      <c r="V245" s="147"/>
-      <c r="W245" s="146"/>
-      <c r="X245" s="147"/>
-      <c r="Y245" s="146"/>
-      <c r="Z245" s="147"/>
-      <c r="AA245" s="148"/>
-      <c r="AB245" s="39"/>
-      <c r="AC245" s="135"/>
-      <c r="AD245" s="39"/>
-      <c r="AE245" s="135"/>
-      <c r="AF245" s="62">
+      <c r="P247" s="147"/>
+      <c r="Q247" s="146"/>
+      <c r="R247" s="147"/>
+      <c r="S247" s="146"/>
+      <c r="T247" s="147"/>
+      <c r="U247" s="146"/>
+      <c r="V247" s="147"/>
+      <c r="W247" s="146"/>
+      <c r="X247" s="147"/>
+      <c r="Y247" s="146"/>
+      <c r="Z247" s="147"/>
+      <c r="AA247" s="148"/>
+      <c r="AB247" s="39"/>
+      <c r="AC247" s="135"/>
+      <c r="AD247" s="39"/>
+      <c r="AE247" s="135"/>
+      <c r="AF247" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>14200</v>
       </c>
-      <c r="AG245" s="63">
+      <c r="AG247" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>8520</v>
       </c>
-      <c r="AH245" s="63">
+      <c r="AH247" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>8520</v>
       </c>
-      <c r="AI245" s="63">
+      <c r="AI247" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>5680</v>
       </c>
-      <c r="AJ245" s="63">
+      <c r="AJ247" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>5680</v>
       </c>
-      <c r="AK245" s="63">
+      <c r="AK247" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL245" s="63">
+      <c r="AL247" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM245" s="63">
+      <c r="AM247" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN245" s="64">
+      <c r="AN247" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO245" s="64">
+      <c r="AO247" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>14200</v>
       </c>
-      <c r="AP245" s="64">
+      <c r="AP247" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>14200</v>
       </c>
-      <c r="AQ245" s="64">
+      <c r="AQ247" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AR245" s="64">
+      <c r="AR247" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS245" s="14">
+      <c r="AS247" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>14200</v>
-      </c>
-      <c r="AT245" s="88"/>
-    </row>
-    <row r="246" spans="1:46" ht="45" x14ac:dyDescent="0.25">
-      <c r="A246" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B246" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="C246" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="D246" s="69" t="s">
-        <v>148</v>
-      </c>
-      <c r="E246" s="67">
-        <v>96</v>
-      </c>
-      <c r="F246" s="68">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G246" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="H246" s="125"/>
-      <c r="I246" s="126"/>
-      <c r="J246" s="125"/>
-      <c r="K246" s="126"/>
-      <c r="L246" s="125"/>
-      <c r="M246" s="126"/>
-      <c r="N246" s="125"/>
-      <c r="O246" s="126"/>
-      <c r="P246" s="125"/>
-      <c r="Q246" s="126"/>
-      <c r="R246" s="125">
-        <v>15000</v>
-      </c>
-      <c r="S246" s="126">
-        <v>15000</v>
-      </c>
-      <c r="T246" s="125">
-        <v>7500</v>
-      </c>
-      <c r="U246" s="126">
-        <v>7500</v>
-      </c>
-      <c r="V246" s="125">
-        <v>7500</v>
-      </c>
-      <c r="W246" s="126">
-        <v>7500</v>
-      </c>
-      <c r="X246" s="125">
-        <v>7500</v>
-      </c>
-      <c r="Y246" s="126">
-        <v>7500</v>
-      </c>
-      <c r="Z246" s="125"/>
-      <c r="AA246" s="126"/>
-      <c r="AB246" s="125"/>
-      <c r="AC246" s="126"/>
-      <c r="AD246" s="125"/>
-      <c r="AE246" s="126"/>
-      <c r="AF246" s="71">
-        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>37500</v>
-      </c>
-      <c r="AG246" s="63">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AH246" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AI246" s="63">
-        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>15000</v>
-      </c>
-      <c r="AJ246" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>15000</v>
-      </c>
-      <c r="AK246" s="63">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>22500</v>
-      </c>
-      <c r="AL246" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>22500</v>
-      </c>
-      <c r="AM246" s="63">
-        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AN246" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AO246" s="72">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>15000</v>
-      </c>
-      <c r="AP246" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>15000</v>
-      </c>
-      <c r="AQ246" s="72">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>22500</v>
-      </c>
-      <c r="AR246" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>22500</v>
-      </c>
-      <c r="AS246" s="73">
-        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>37500</v>
-      </c>
-      <c r="AT246" s="88"/>
-    </row>
-    <row r="247" spans="1:46" ht="45" x14ac:dyDescent="0.25">
-      <c r="A247" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B247" s="65" t="s">
-        <v>178</v>
-      </c>
-      <c r="C247" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="D247" s="69" t="s">
-        <v>148</v>
-      </c>
-      <c r="E247" s="67">
-        <v>96</v>
-      </c>
-      <c r="F247" s="68">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G247" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="H247" s="125"/>
-      <c r="I247" s="126"/>
-      <c r="J247" s="125"/>
-      <c r="K247" s="126"/>
-      <c r="L247" s="125"/>
-      <c r="M247" s="126"/>
-      <c r="N247" s="125"/>
-      <c r="O247" s="126"/>
-      <c r="P247" s="125"/>
-      <c r="Q247" s="126"/>
-      <c r="R247" s="125"/>
-      <c r="S247" s="126"/>
-      <c r="T247" s="125"/>
-      <c r="U247" s="126"/>
-      <c r="V247" s="125"/>
-      <c r="W247" s="126"/>
-      <c r="X247" s="125"/>
-      <c r="Y247" s="126"/>
-      <c r="Z247" s="125">
-        <v>7500</v>
-      </c>
-      <c r="AA247" s="126"/>
-      <c r="AB247" s="125"/>
-      <c r="AC247" s="126"/>
-      <c r="AD247" s="125"/>
-      <c r="AE247" s="126"/>
-      <c r="AF247" s="71">
-        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7500</v>
-      </c>
-      <c r="AG247" s="63">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AH247" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AI247" s="63">
-        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AJ247" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AK247" s="63">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AL247" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AM247" s="63">
-        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7500</v>
-      </c>
-      <c r="AN247" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AO247" s="72">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AP247" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AQ247" s="72">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>7500</v>
-      </c>
-      <c r="AR247" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS247" s="73">
-        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
       </c>
       <c r="AT247" s="88"/>
     </row>
     <row r="248" spans="1:46" ht="45" x14ac:dyDescent="0.25">
-      <c r="A248" s="74" t="s">
+      <c r="A248" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B248" s="65" t="s">
-        <v>179</v>
-      </c>
-      <c r="C248" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C248" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="D248" s="59" t="s">
+      <c r="D248" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E248" s="60">
+      <c r="E248" s="67">
         <v>96</v>
       </c>
-      <c r="F248" s="61">
+      <c r="F248" s="68">
         <v>2.2999999999999998</v>
       </c>
       <c r="G248" s="59" t="s">
-        <v>70</v>
-      </c>
-      <c r="H248" s="145"/>
-      <c r="I248" s="146"/>
-      <c r="J248" s="147"/>
-      <c r="K248" s="146"/>
-      <c r="L248" s="147">
-        <v>6000</v>
-      </c>
-      <c r="M248" s="146">
-        <v>6000</v>
-      </c>
-      <c r="N248" s="147"/>
-      <c r="O248" s="146"/>
-      <c r="P248" s="147">
-        <v>14000</v>
-      </c>
-      <c r="Q248" s="146">
-        <v>14000</v>
-      </c>
-      <c r="R248" s="147"/>
-      <c r="S248" s="146"/>
-      <c r="T248" s="147"/>
-      <c r="U248" s="146"/>
-      <c r="V248" s="147"/>
-      <c r="W248" s="146"/>
-      <c r="X248" s="147"/>
-      <c r="Y248" s="146"/>
-      <c r="Z248" s="147"/>
-      <c r="AA248" s="148"/>
-      <c r="AB248" s="39"/>
-      <c r="AC248" s="135"/>
-      <c r="AD248" s="39"/>
-      <c r="AE248" s="135"/>
-      <c r="AF248" s="62">
+        <v>57</v>
+      </c>
+      <c r="H248" s="125"/>
+      <c r="I248" s="126"/>
+      <c r="J248" s="125"/>
+      <c r="K248" s="126"/>
+      <c r="L248" s="125"/>
+      <c r="M248" s="126"/>
+      <c r="N248" s="125"/>
+      <c r="O248" s="126"/>
+      <c r="P248" s="125"/>
+      <c r="Q248" s="126"/>
+      <c r="R248" s="125">
+        <v>15000</v>
+      </c>
+      <c r="S248" s="126">
+        <v>15000</v>
+      </c>
+      <c r="T248" s="125">
+        <v>7500</v>
+      </c>
+      <c r="U248" s="126">
+        <v>7500</v>
+      </c>
+      <c r="V248" s="125">
+        <v>7500</v>
+      </c>
+      <c r="W248" s="126">
+        <v>7500</v>
+      </c>
+      <c r="X248" s="125">
+        <v>7500</v>
+      </c>
+      <c r="Y248" s="126">
+        <v>7500</v>
+      </c>
+      <c r="Z248" s="125"/>
+      <c r="AA248" s="126"/>
+      <c r="AB248" s="125"/>
+      <c r="AC248" s="126"/>
+      <c r="AD248" s="125"/>
+      <c r="AE248" s="126"/>
+      <c r="AF248" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>20000</v>
+        <v>37500</v>
       </c>
       <c r="AG248" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AH248" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AI248" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="AJ248" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="AK248" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="AL248" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="AM248" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN248" s="64">
+      <c r="AN248" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO248" s="64">
+      <c r="AO248" s="72">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>20000</v>
-      </c>
-      <c r="AP248" s="64">
+        <v>15000</v>
+      </c>
+      <c r="AP248" s="72">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>20000</v>
-      </c>
-      <c r="AQ248" s="64">
+        <v>15000</v>
+      </c>
+      <c r="AQ248" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AR248" s="64">
+        <v>22500</v>
+      </c>
+      <c r="AR248" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS248" s="14">
+        <v>22500</v>
+      </c>
+      <c r="AS248" s="73">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>20000</v>
+        <v>37500</v>
       </c>
       <c r="AT248" s="88"/>
     </row>
-    <row r="249" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A249" s="74" t="s">
+    <row r="249" spans="1:46" ht="45" x14ac:dyDescent="0.25">
+      <c r="A249" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B249" s="65" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="C249" s="66" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="D249" s="69" t="s">
         <v>148</v>
@@ -32072,8 +32117,8 @@
       <c r="F249" s="68">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G249" s="69" t="s">
-        <v>183</v>
+      <c r="G249" s="59" t="s">
+        <v>57</v>
       </c>
       <c r="H249" s="125"/>
       <c r="I249" s="126"/>
@@ -32094,400 +32139,404 @@
       <c r="X249" s="125"/>
       <c r="Y249" s="126"/>
       <c r="Z249" s="125">
-        <v>1973.8</v>
+        <v>7500</v>
       </c>
       <c r="AA249" s="126"/>
       <c r="AB249" s="125"/>
       <c r="AC249" s="126"/>
       <c r="AD249" s="125"/>
       <c r="AE249" s="126"/>
-      <c r="AF249" s="23">
+      <c r="AF249" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1973.8</v>
-      </c>
-      <c r="AG249" s="23">
+        <v>7500</v>
+      </c>
+      <c r="AG249" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH249" s="23">
+      <c r="AH249" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI249" s="23">
+      <c r="AI249" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ249" s="23">
+      <c r="AJ249" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK249" s="23">
+      <c r="AK249" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL249" s="23">
+      <c r="AL249" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM249" s="23">
+      <c r="AM249" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1973.8</v>
-      </c>
-      <c r="AN249" s="14">
+        <v>7500</v>
+      </c>
+      <c r="AN249" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO249" s="14">
+      <c r="AO249" s="72">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP249" s="14">
+      <c r="AP249" s="72">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ249" s="14">
+      <c r="AQ249" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1973.8</v>
-      </c>
-      <c r="AR249" s="14">
+        <v>7500</v>
+      </c>
+      <c r="AR249" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS249" s="23">
+      <c r="AS249" s="73">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
       <c r="AT249" s="88"/>
     </row>
-    <row r="250" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A250" s="70" t="s">
+    <row r="250" spans="1:46" ht="45" x14ac:dyDescent="0.25">
+      <c r="A250" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B250" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="C250" s="66" t="s">
+        <v>178</v>
+      </c>
+      <c r="C250" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="D250" s="69" t="s">
+      <c r="D250" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E250" s="67">
+      <c r="E250" s="60">
         <v>96</v>
       </c>
-      <c r="F250" s="68">
+      <c r="F250" s="61">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G250" s="69" t="s">
+      <c r="G250" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="H250" s="145"/>
+      <c r="I250" s="146"/>
+      <c r="J250" s="147"/>
+      <c r="K250" s="146"/>
+      <c r="L250" s="147">
+        <v>6000</v>
+      </c>
+      <c r="M250" s="146">
+        <v>6000</v>
+      </c>
+      <c r="N250" s="147"/>
+      <c r="O250" s="146"/>
+      <c r="P250" s="147">
+        <v>14000</v>
+      </c>
+      <c r="Q250" s="146">
+        <v>14000</v>
+      </c>
+      <c r="R250" s="147"/>
+      <c r="S250" s="146"/>
+      <c r="T250" s="147"/>
+      <c r="U250" s="146"/>
+      <c r="V250" s="147"/>
+      <c r="W250" s="146"/>
+      <c r="X250" s="147"/>
+      <c r="Y250" s="146"/>
+      <c r="Z250" s="147"/>
+      <c r="AA250" s="148"/>
+      <c r="AB250" s="39"/>
+      <c r="AC250" s="135"/>
+      <c r="AD250" s="39"/>
+      <c r="AE250" s="135"/>
+      <c r="AF250" s="62">
+        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>20000</v>
+      </c>
+      <c r="AG250" s="63">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
+        <v>6000</v>
+      </c>
+      <c r="AH250" s="63">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
+        <v>6000</v>
+      </c>
+      <c r="AI250" s="63">
+        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>14000</v>
+      </c>
+      <c r="AJ250" s="63">
+        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>14000</v>
+      </c>
+      <c r="AK250" s="63">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AL250" s="63">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AM250" s="63">
+        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AN250" s="64">
+        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AO250" s="64">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>20000</v>
+      </c>
+      <c r="AP250" s="64">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>20000</v>
+      </c>
+      <c r="AQ250" s="64">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AR250" s="64">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AS250" s="14">
+        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>20000</v>
+      </c>
+      <c r="AT250" s="88"/>
+    </row>
+    <row r="251" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A251" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="B251" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="C251" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D251" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="E251" s="67">
+        <v>96</v>
+      </c>
+      <c r="F251" s="68">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G251" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="H250" s="125"/>
-      <c r="I250" s="126"/>
-      <c r="J250" s="125"/>
-      <c r="K250" s="126"/>
-      <c r="L250" s="125"/>
-      <c r="M250" s="126"/>
-      <c r="N250" s="125"/>
-      <c r="O250" s="126"/>
-      <c r="P250" s="125"/>
-      <c r="Q250" s="126"/>
-      <c r="R250" s="125"/>
-      <c r="S250" s="126"/>
-      <c r="T250" s="125"/>
-      <c r="U250" s="126"/>
-      <c r="V250" s="125">
+      <c r="H251" s="125"/>
+      <c r="I251" s="126"/>
+      <c r="J251" s="125"/>
+      <c r="K251" s="126"/>
+      <c r="L251" s="125"/>
+      <c r="M251" s="126"/>
+      <c r="N251" s="125"/>
+      <c r="O251" s="126"/>
+      <c r="P251" s="125"/>
+      <c r="Q251" s="126"/>
+      <c r="R251" s="125"/>
+      <c r="S251" s="126"/>
+      <c r="T251" s="125"/>
+      <c r="U251" s="126"/>
+      <c r="V251" s="125">
         <v>6000</v>
       </c>
-      <c r="W250" s="126">
+      <c r="W251" s="126">
         <v>6000</v>
       </c>
-      <c r="X250" s="125">
+      <c r="X251" s="125">
         <v>6000</v>
       </c>
-      <c r="Y250" s="126">
+      <c r="Y251" s="126">
         <v>6000</v>
       </c>
-      <c r="Z250" s="125"/>
-      <c r="AA250" s="126"/>
-      <c r="AB250" s="125"/>
-      <c r="AC250" s="126"/>
-      <c r="AD250" s="125"/>
-      <c r="AE250" s="126"/>
-      <c r="AF250" s="71">
+      <c r="Z251" s="125"/>
+      <c r="AA251" s="126"/>
+      <c r="AB251" s="125"/>
+      <c r="AC251" s="126"/>
+      <c r="AD251" s="125"/>
+      <c r="AE251" s="126"/>
+      <c r="AF251" s="71">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AG250" s="63">
+      <c r="AG251" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH250" s="63">
+      <c r="AH251" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI250" s="63">
+      <c r="AI251" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ250" s="63">
+      <c r="AJ251" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK250" s="63">
+      <c r="AK251" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AL250" s="63">
+      <c r="AL251" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AM250" s="63">
+      <c r="AM251" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN250" s="72">
+      <c r="AN251" s="72">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO250" s="72">
+      <c r="AO251" s="72">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP250" s="72">
+      <c r="AP251" s="72">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ250" s="72">
+      <c r="AQ251" s="72">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AR250" s="72">
+      <c r="AR251" s="72">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AS250" s="73">
+      <c r="AS251" s="73">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AT250" s="88"/>
+      <c r="AT251" s="88"/>
     </row>
-    <row r="251" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A251" s="74" t="s">
+    <row r="252" spans="1:46" ht="30" x14ac:dyDescent="0.25">
+      <c r="A252" s="74" t="s">
         <v>146</v>
       </c>
-      <c r="B251" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="C251" s="59" t="s">
+      <c r="B252" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C252" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="D251" s="59" t="s">
+      <c r="D252" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E251" s="60">
+      <c r="E252" s="60">
         <v>96</v>
       </c>
-      <c r="F251" s="61">
+      <c r="F252" s="61">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G251" s="59" t="s">
+      <c r="G252" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H251" s="145"/>
-      <c r="I251" s="146"/>
-      <c r="J251" s="147"/>
-      <c r="K251" s="146"/>
-      <c r="L251" s="147">
+      <c r="H252" s="145"/>
+      <c r="I252" s="146"/>
+      <c r="J252" s="147"/>
+      <c r="K252" s="146"/>
+      <c r="L252" s="147">
         <v>6480</v>
       </c>
-      <c r="M251" s="146">
+      <c r="M252" s="146">
         <v>6480</v>
       </c>
-      <c r="N251" s="147">
+      <c r="N252" s="147">
         <v>15120</v>
       </c>
-      <c r="O251" s="146">
+      <c r="O252" s="146">
         <v>15120</v>
       </c>
-      <c r="P251" s="147"/>
-      <c r="Q251" s="146"/>
-      <c r="R251" s="147"/>
-      <c r="S251" s="146"/>
-      <c r="T251" s="147"/>
-      <c r="U251" s="146"/>
-      <c r="V251" s="147"/>
-      <c r="W251" s="146"/>
-      <c r="X251" s="147"/>
-      <c r="Y251" s="146"/>
-      <c r="Z251" s="147"/>
-      <c r="AA251" s="148"/>
-      <c r="AB251" s="39"/>
-      <c r="AC251" s="135"/>
-      <c r="AD251" s="39"/>
-      <c r="AE251" s="135"/>
-      <c r="AF251" s="62">
+      <c r="P252" s="147"/>
+      <c r="Q252" s="146"/>
+      <c r="R252" s="147"/>
+      <c r="S252" s="146"/>
+      <c r="T252" s="147"/>
+      <c r="U252" s="146"/>
+      <c r="V252" s="147"/>
+      <c r="W252" s="146"/>
+      <c r="X252" s="147"/>
+      <c r="Y252" s="146"/>
+      <c r="Z252" s="147"/>
+      <c r="AA252" s="148"/>
+      <c r="AB252" s="39"/>
+      <c r="AC252" s="135"/>
+      <c r="AD252" s="39"/>
+      <c r="AE252" s="135"/>
+      <c r="AF252" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>21600</v>
       </c>
-      <c r="AG251" s="63">
+      <c r="AG252" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>6480</v>
       </c>
-      <c r="AH251" s="63">
+      <c r="AH252" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>6480</v>
       </c>
-      <c r="AI251" s="63">
+      <c r="AI252" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>15120</v>
       </c>
-      <c r="AJ251" s="63">
+      <c r="AJ252" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>15120</v>
       </c>
-      <c r="AK251" s="63">
+      <c r="AK252" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL251" s="63">
+      <c r="AL252" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM251" s="63">
+      <c r="AM252" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN251" s="64">
+      <c r="AN252" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO251" s="64">
+      <c r="AO252" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>21600</v>
       </c>
-      <c r="AP251" s="64">
+      <c r="AP252" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>21600</v>
       </c>
-      <c r="AQ251" s="64">
+      <c r="AQ252" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AR251" s="64">
+      <c r="AR252" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS251" s="14">
+      <c r="AS252" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>21600</v>
-      </c>
-      <c r="AT251" s="88"/>
-    </row>
-    <row r="252" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A252" s="74" t="s">
-        <v>146</v>
-      </c>
-      <c r="B252" s="65" t="s">
-        <v>181</v>
-      </c>
-      <c r="C252" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="D252" s="69" t="s">
-        <v>148</v>
-      </c>
-      <c r="E252" s="67">
-        <v>96</v>
-      </c>
-      <c r="F252" s="68">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G252" s="69" t="s">
-        <v>183</v>
-      </c>
-      <c r="H252" s="125"/>
-      <c r="I252" s="126"/>
-      <c r="J252" s="125"/>
-      <c r="K252" s="126"/>
-      <c r="L252" s="125"/>
-      <c r="M252" s="126"/>
-      <c r="N252" s="125"/>
-      <c r="O252" s="126"/>
-      <c r="P252" s="125"/>
-      <c r="Q252" s="126"/>
-      <c r="R252" s="125"/>
-      <c r="S252" s="126"/>
-      <c r="T252" s="125">
-        <v>228.6</v>
-      </c>
-      <c r="U252" s="126">
-        <v>228.6</v>
-      </c>
-      <c r="V252" s="125"/>
-      <c r="W252" s="126"/>
-      <c r="X252" s="125"/>
-      <c r="Y252" s="126"/>
-      <c r="Z252" s="125"/>
-      <c r="AA252" s="126"/>
-      <c r="AB252" s="125"/>
-      <c r="AC252" s="126"/>
-      <c r="AD252" s="125"/>
-      <c r="AE252" s="126"/>
-      <c r="AF252" s="63">
-        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>228.6</v>
-      </c>
-      <c r="AG252" s="63">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AH252" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AI252" s="63">
-        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AJ252" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AK252" s="63">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>228.6</v>
-      </c>
-      <c r="AL252" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>228.6</v>
-      </c>
-      <c r="AM252" s="63">
-        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AN252" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AO252" s="63">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AP252" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AQ252" s="63">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>228.6</v>
-      </c>
-      <c r="AR252" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>228.6</v>
-      </c>
-      <c r="AS252" s="23">
-        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>228.6</v>
       </c>
       <c r="AT252" s="88"/>
     </row>
@@ -32496,54 +32545,54 @@
         <v>146</v>
       </c>
       <c r="B253" s="65" t="s">
-        <v>184</v>
-      </c>
-      <c r="C253" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="C253" s="66" t="s">
+        <v>181</v>
+      </c>
+      <c r="D253" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="E253" s="67">
+        <v>96</v>
+      </c>
+      <c r="F253" s="68">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G253" s="69" t="s">
         <v>182</v>
       </c>
-      <c r="D253" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="E253" s="60">
-        <v>96</v>
-      </c>
-      <c r="F253" s="61">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G253" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="H253" s="145"/>
-      <c r="I253" s="146"/>
-      <c r="J253" s="147"/>
-      <c r="K253" s="146"/>
-      <c r="L253" s="147"/>
-      <c r="M253" s="146"/>
-      <c r="N253" s="147"/>
-      <c r="O253" s="146"/>
-      <c r="P253" s="147"/>
-      <c r="Q253" s="146"/>
-      <c r="R253" s="147"/>
-      <c r="S253" s="146"/>
-      <c r="T253" s="147">
-        <v>30671.4</v>
-      </c>
-      <c r="U253" s="146">
-        <v>30671.4</v>
-      </c>
-      <c r="V253" s="147"/>
-      <c r="W253" s="146"/>
-      <c r="X253" s="147"/>
-      <c r="Y253" s="146"/>
-      <c r="Z253" s="147"/>
-      <c r="AA253" s="148"/>
-      <c r="AB253" s="39"/>
-      <c r="AC253" s="135"/>
-      <c r="AD253" s="39"/>
-      <c r="AE253" s="135"/>
-      <c r="AF253" s="62">
+      <c r="H253" s="125"/>
+      <c r="I253" s="126"/>
+      <c r="J253" s="125"/>
+      <c r="K253" s="126"/>
+      <c r="L253" s="125"/>
+      <c r="M253" s="126"/>
+      <c r="N253" s="125"/>
+      <c r="O253" s="126"/>
+      <c r="P253" s="125"/>
+      <c r="Q253" s="126"/>
+      <c r="R253" s="125"/>
+      <c r="S253" s="126"/>
+      <c r="T253" s="125">
+        <v>228.6</v>
+      </c>
+      <c r="U253" s="126">
+        <v>228.6</v>
+      </c>
+      <c r="V253" s="125"/>
+      <c r="W253" s="126"/>
+      <c r="X253" s="125"/>
+      <c r="Y253" s="126"/>
+      <c r="Z253" s="125"/>
+      <c r="AA253" s="126"/>
+      <c r="AB253" s="125"/>
+      <c r="AC253" s="126"/>
+      <c r="AD253" s="125"/>
+      <c r="AE253" s="126"/>
+      <c r="AF253" s="63">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>30671.4</v>
+        <v>228.6</v>
       </c>
       <c r="AG253" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -32563,39 +32612,39 @@
       </c>
       <c r="AK253" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>30671.4</v>
+        <v>228.6</v>
       </c>
       <c r="AL253" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>30671.4</v>
+        <v>228.6</v>
       </c>
       <c r="AM253" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN253" s="64">
+      <c r="AN253" s="63">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO253" s="64">
+      <c r="AO253" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP253" s="64">
+      <c r="AP253" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ253" s="64">
+      <c r="AQ253" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>30671.4</v>
-      </c>
-      <c r="AR253" s="64">
+        <v>228.6</v>
+      </c>
+      <c r="AR253" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>30671.4</v>
-      </c>
-      <c r="AS253" s="14">
+        <v>228.6</v>
+      </c>
+      <c r="AS253" s="23">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>30671.4</v>
+        <v>228.6</v>
       </c>
       <c r="AT253" s="88"/>
     </row>
@@ -32604,10 +32653,10 @@
         <v>146</v>
       </c>
       <c r="B254" s="65" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="C254" s="59" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c r="D254" s="59" t="s">
         <v>148</v>
@@ -32619,20 +32668,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G254" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="H254" s="145">
-        <v>7380</v>
-      </c>
-      <c r="I254" s="146">
-        <v>7380</v>
-      </c>
-      <c r="J254" s="147">
-        <v>7380</v>
-      </c>
-      <c r="K254" s="146">
-        <v>7380</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="H254" s="145"/>
+      <c r="I254" s="146"/>
+      <c r="J254" s="147"/>
+      <c r="K254" s="146"/>
       <c r="L254" s="147"/>
       <c r="M254" s="146"/>
       <c r="N254" s="147"/>
@@ -32641,8 +32682,12 @@
       <c r="Q254" s="146"/>
       <c r="R254" s="147"/>
       <c r="S254" s="146"/>
-      <c r="T254" s="147"/>
-      <c r="U254" s="146"/>
+      <c r="T254" s="147">
+        <v>30671.4</v>
+      </c>
+      <c r="U254" s="146">
+        <v>30671.4</v>
+      </c>
       <c r="V254" s="147"/>
       <c r="W254" s="146"/>
       <c r="X254" s="147"/>
@@ -32655,15 +32700,15 @@
       <c r="AE254" s="135"/>
       <c r="AF254" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>14760</v>
+        <v>30671.4</v>
       </c>
       <c r="AG254" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="AH254" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="AI254" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -32675,11 +32720,11 @@
       </c>
       <c r="AK254" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>30671.4</v>
       </c>
       <c r="AL254" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>30671.4</v>
       </c>
       <c r="AM254" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -32691,23 +32736,23 @@
       </c>
       <c r="AO254" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="AP254" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="AQ254" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
+        <v>30671.4</v>
       </c>
       <c r="AR254" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>30671.4</v>
       </c>
       <c r="AS254" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>14760</v>
+        <v>30671.4</v>
       </c>
       <c r="AT254" s="88"/>
     </row>
@@ -32716,7 +32761,7 @@
         <v>146</v>
       </c>
       <c r="B255" s="65" t="s">
-        <v>185</v>
+        <v>63</v>
       </c>
       <c r="C255" s="59" t="s">
         <v>56</v>
@@ -32733,13 +32778,17 @@
       <c r="G255" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H255" s="145"/>
-      <c r="I255" s="146"/>
+      <c r="H255" s="145">
+        <v>7380</v>
+      </c>
+      <c r="I255" s="146">
+        <v>7380</v>
+      </c>
       <c r="J255" s="147">
-        <v>6001.2</v>
+        <v>7380</v>
       </c>
       <c r="K255" s="146">
-        <v>6001.2</v>
+        <v>7380</v>
       </c>
       <c r="L255" s="147"/>
       <c r="M255" s="146"/>
@@ -32763,15 +32812,15 @@
       <c r="AE255" s="135"/>
       <c r="AF255" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>6001.2</v>
+        <v>14760</v>
       </c>
       <c r="AG255" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>6001.2</v>
+        <v>14760</v>
       </c>
       <c r="AH255" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>6001.2</v>
+        <v>14760</v>
       </c>
       <c r="AI255" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -32799,11 +32848,11 @@
       </c>
       <c r="AO255" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>6001.2</v>
+        <v>14760</v>
       </c>
       <c r="AP255" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>6001.2</v>
+        <v>14760</v>
       </c>
       <c r="AQ255" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -32815,7 +32864,7 @@
       </c>
       <c r="AS255" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>6001.2</v>
+        <v>14760</v>
       </c>
       <c r="AT255" s="88"/>
     </row>
@@ -32824,7 +32873,7 @@
         <v>146</v>
       </c>
       <c r="B256" s="65" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C256" s="59" t="s">
         <v>56</v>
@@ -32843,20 +32892,16 @@
       </c>
       <c r="H256" s="145"/>
       <c r="I256" s="146"/>
-      <c r="J256" s="147"/>
-      <c r="K256" s="146"/>
-      <c r="L256" s="147">
-        <v>6000</v>
-      </c>
-      <c r="M256" s="146">
-        <v>6000</v>
-      </c>
-      <c r="N256" s="147">
-        <v>6000</v>
-      </c>
-      <c r="O256" s="146">
-        <v>6000</v>
-      </c>
+      <c r="J256" s="147">
+        <v>6001.2</v>
+      </c>
+      <c r="K256" s="146">
+        <v>6001.2</v>
+      </c>
+      <c r="L256" s="147"/>
+      <c r="M256" s="146"/>
+      <c r="N256" s="147"/>
+      <c r="O256" s="146"/>
       <c r="P256" s="147"/>
       <c r="Q256" s="146"/>
       <c r="R256" s="147"/>
@@ -32875,23 +32920,23 @@
       <c r="AE256" s="135"/>
       <c r="AF256" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>12000</v>
+        <v>6001.2</v>
       </c>
       <c r="AG256" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>6000</v>
+        <v>6001.2</v>
       </c>
       <c r="AH256" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>6000</v>
+        <v>6001.2</v>
       </c>
       <c r="AI256" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AJ256" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AK256" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
@@ -32911,11 +32956,11 @@
       </c>
       <c r="AO256" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>12000</v>
+        <v>6001.2</v>
       </c>
       <c r="AP256" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>12000</v>
+        <v>6001.2</v>
       </c>
       <c r="AQ256" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -32927,146 +32972,142 @@
       </c>
       <c r="AS256" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>12000</v>
+        <v>6001.2</v>
       </c>
       <c r="AT256" s="88"/>
     </row>
     <row r="257" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A257" s="70" t="s">
+      <c r="A257" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B257" s="65" t="s">
-        <v>187</v>
-      </c>
-      <c r="C257" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="C257" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="D257" s="69" t="s">
+      <c r="D257" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E257" s="67">
+      <c r="E257" s="60">
         <v>96</v>
       </c>
-      <c r="F257" s="68">
+      <c r="F257" s="61">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G257" s="69" t="s">
+      <c r="G257" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H257" s="125"/>
-      <c r="I257" s="126"/>
-      <c r="J257" s="125"/>
-      <c r="K257" s="126"/>
-      <c r="L257" s="125"/>
-      <c r="M257" s="126"/>
-      <c r="N257" s="125"/>
-      <c r="O257" s="126"/>
-      <c r="P257" s="125"/>
-      <c r="Q257" s="126"/>
-      <c r="R257" s="125">
+      <c r="H257" s="145"/>
+      <c r="I257" s="146"/>
+      <c r="J257" s="147"/>
+      <c r="K257" s="146"/>
+      <c r="L257" s="147">
+        <v>6000</v>
+      </c>
+      <c r="M257" s="146">
+        <v>6000</v>
+      </c>
+      <c r="N257" s="147">
+        <v>6000</v>
+      </c>
+      <c r="O257" s="146">
+        <v>6000</v>
+      </c>
+      <c r="P257" s="147"/>
+      <c r="Q257" s="146"/>
+      <c r="R257" s="147"/>
+      <c r="S257" s="146"/>
+      <c r="T257" s="147"/>
+      <c r="U257" s="146"/>
+      <c r="V257" s="147"/>
+      <c r="W257" s="146"/>
+      <c r="X257" s="147"/>
+      <c r="Y257" s="146"/>
+      <c r="Z257" s="147"/>
+      <c r="AA257" s="148"/>
+      <c r="AB257" s="39"/>
+      <c r="AC257" s="135"/>
+      <c r="AD257" s="39"/>
+      <c r="AE257" s="135"/>
+      <c r="AF257" s="62">
+        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>12000</v>
-      </c>
-      <c r="S257" s="126">
-        <v>12000</v>
-      </c>
-      <c r="T257" s="125">
-        <v>6000</v>
-      </c>
-      <c r="U257" s="126">
-        <v>6000</v>
-      </c>
-      <c r="V257" s="125">
-        <v>6000</v>
-      </c>
-      <c r="W257" s="126">
-        <v>6000</v>
-      </c>
-      <c r="X257" s="125"/>
-      <c r="Y257" s="126"/>
-      <c r="Z257" s="125"/>
-      <c r="AA257" s="126"/>
-      <c r="AB257" s="125"/>
-      <c r="AC257" s="126"/>
-      <c r="AD257" s="125"/>
-      <c r="AE257" s="126"/>
-      <c r="AF257" s="71">
-        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>24000</v>
       </c>
       <c r="AG257" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AH257" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AI257" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="AJ257" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="AK257" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AL257" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AM257" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN257" s="72">
+      <c r="AN257" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO257" s="72">
+      <c r="AO257" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>12000</v>
       </c>
-      <c r="AP257" s="72">
+      <c r="AP257" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>12000</v>
       </c>
-      <c r="AQ257" s="72">
+      <c r="AQ257" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AR257" s="64">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AS257" s="14">
+        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>12000</v>
-      </c>
-      <c r="AR257" s="72">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>12000</v>
-      </c>
-      <c r="AS257" s="73">
-        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>24000</v>
       </c>
       <c r="AT257" s="88"/>
     </row>
     <row r="258" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A258" s="161" t="s">
+      <c r="A258" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="B258" s="165" t="s">
-        <v>249</v>
-      </c>
-      <c r="C258" s="163" t="s">
-        <v>245</v>
-      </c>
-      <c r="D258" s="163" t="s">
+      <c r="B258" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C258" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D258" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E258" s="166">
+      <c r="E258" s="67">
         <v>96</v>
       </c>
-      <c r="F258" s="167">
-        <v>23</v>
-      </c>
-      <c r="G258" s="163" t="s">
+      <c r="F258" s="68">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G258" s="69" t="s">
         <v>57</v>
       </c>
       <c r="H258" s="125"/>
@@ -33079,205 +33120,209 @@
       <c r="O258" s="126"/>
       <c r="P258" s="125"/>
       <c r="Q258" s="126"/>
-      <c r="R258" s="125"/>
-      <c r="S258" s="126"/>
-      <c r="T258" s="125"/>
-      <c r="U258" s="126"/>
-      <c r="V258" s="125"/>
-      <c r="W258" s="126"/>
-      <c r="X258" s="125">
+      <c r="R258" s="125">
+        <v>12000</v>
+      </c>
+      <c r="S258" s="126">
+        <v>12000</v>
+      </c>
+      <c r="T258" s="125">
         <v>6000</v>
       </c>
-      <c r="Y258" s="126">
+      <c r="U258" s="126">
         <v>6000</v>
       </c>
-      <c r="Z258" s="125">
+      <c r="V258" s="125">
         <v>6000</v>
       </c>
+      <c r="W258" s="126">
+        <v>6000</v>
+      </c>
+      <c r="X258" s="125"/>
+      <c r="Y258" s="126"/>
+      <c r="Z258" s="125"/>
       <c r="AA258" s="126"/>
       <c r="AB258" s="125"/>
       <c r="AC258" s="126"/>
       <c r="AD258" s="125"/>
       <c r="AE258" s="126"/>
-      <c r="AF258" s="63">
+      <c r="AF258" s="71">
+        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>24000</v>
+      </c>
+      <c r="AG258" s="63">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AH258" s="63">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
+        <v>0</v>
+      </c>
+      <c r="AI258" s="63">
+        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AJ258" s="63">
+        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AK258" s="63">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AL258" s="63">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AM258" s="63">
+        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AN258" s="72">
+        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>0</v>
+      </c>
+      <c r="AO258" s="72">
+        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AP258" s="72">
+        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AQ258" s="72">
+        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AR258" s="72">
+        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>12000</v>
+      </c>
+      <c r="AS258" s="73">
+        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
+        <v>24000</v>
+      </c>
+      <c r="AT258" s="88"/>
+    </row>
+    <row r="259" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A259" s="161" t="s">
+        <v>146</v>
+      </c>
+      <c r="B259" s="165" t="s">
+        <v>246</v>
+      </c>
+      <c r="C259" s="163" t="s">
+        <v>243</v>
+      </c>
+      <c r="D259" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="E259" s="166">
+        <v>96</v>
+      </c>
+      <c r="F259" s="167">
+        <v>23</v>
+      </c>
+      <c r="G259" s="163" t="s">
+        <v>57</v>
+      </c>
+      <c r="H259" s="125"/>
+      <c r="I259" s="126"/>
+      <c r="J259" s="125"/>
+      <c r="K259" s="126"/>
+      <c r="L259" s="125"/>
+      <c r="M259" s="126"/>
+      <c r="N259" s="125"/>
+      <c r="O259" s="126"/>
+      <c r="P259" s="125"/>
+      <c r="Q259" s="126"/>
+      <c r="R259" s="125"/>
+      <c r="S259" s="126"/>
+      <c r="T259" s="125"/>
+      <c r="U259" s="126"/>
+      <c r="V259" s="125"/>
+      <c r="W259" s="126"/>
+      <c r="X259" s="125">
+        <v>6000</v>
+      </c>
+      <c r="Y259" s="126">
+        <v>6000</v>
+      </c>
+      <c r="Z259" s="125">
+        <v>6000</v>
+      </c>
+      <c r="AA259" s="126"/>
+      <c r="AB259" s="125"/>
+      <c r="AC259" s="126"/>
+      <c r="AD259" s="125"/>
+      <c r="AE259" s="126"/>
+      <c r="AF259" s="63">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AG258" s="63">
+      <c r="AG259" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH258" s="63">
+      <c r="AH259" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI258" s="63">
+      <c r="AI259" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ258" s="63">
+      <c r="AJ259" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK258" s="63">
+      <c r="AK259" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>6000</v>
       </c>
-      <c r="AL258" s="63">
+      <c r="AL259" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>6000</v>
       </c>
-      <c r="AM258" s="63">
+      <c r="AM259" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>6000</v>
       </c>
-      <c r="AN258" s="64">
+      <c r="AN259" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO258" s="64">
+      <c r="AO259" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP258" s="64">
+      <c r="AP259" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ258" s="64">
+      <c r="AQ259" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>12000</v>
       </c>
-      <c r="AR258" s="64">
+      <c r="AR259" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>6000</v>
       </c>
-      <c r="AS258" s="23">
+      <c r="AS259" s="23">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>6000</v>
       </c>
-      <c r="AT258" s="88"/>
-    </row>
-    <row r="259" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A259" s="74" t="s">
-        <v>146</v>
-      </c>
-      <c r="B259" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="C259" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="D259" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="E259" s="60">
-        <v>97</v>
-      </c>
-      <c r="F259" s="61">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G259" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="H259" s="145">
-        <v>7892.5</v>
-      </c>
-      <c r="I259" s="146">
-        <v>7892.5</v>
-      </c>
-      <c r="J259" s="147"/>
-      <c r="K259" s="146"/>
-      <c r="L259" s="147">
-        <v>7892.5</v>
-      </c>
-      <c r="M259" s="146">
-        <v>7892.5</v>
-      </c>
-      <c r="N259" s="147"/>
-      <c r="O259" s="146"/>
-      <c r="P259" s="147"/>
-      <c r="Q259" s="146"/>
-      <c r="R259" s="147"/>
-      <c r="S259" s="146"/>
-      <c r="T259" s="147"/>
-      <c r="U259" s="146"/>
-      <c r="V259" s="147"/>
-      <c r="W259" s="146"/>
-      <c r="X259" s="147"/>
-      <c r="Y259" s="146"/>
-      <c r="Z259" s="147"/>
-      <c r="AA259" s="148"/>
-      <c r="AB259" s="39"/>
-      <c r="AC259" s="135"/>
-      <c r="AD259" s="39"/>
-      <c r="AE259" s="135"/>
-      <c r="AF259" s="62">
-        <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>15785</v>
-      </c>
-      <c r="AG259" s="63">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>15785</v>
-      </c>
-      <c r="AH259" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>15785</v>
-      </c>
-      <c r="AI259" s="63">
-        <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AJ259" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="AK259" s="63">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AL259" s="63">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AM259" s="63">
-        <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AN259" s="64">
-        <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AO259" s="64">
-        <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>15785</v>
-      </c>
-      <c r="AP259" s="64">
-        <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>15785</v>
-      </c>
-      <c r="AQ259" s="64">
-        <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AR259" s="64">
-        <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS259" s="14">
-        <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>15785</v>
-      </c>
       <c r="AT259" s="88"/>
     </row>
-    <row r="260" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:46" ht="30" x14ac:dyDescent="0.25">
       <c r="A260" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B260" s="65" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C260" s="59" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="D260" s="59" t="s">
         <v>148</v>
@@ -33289,14 +33334,22 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G260" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="H260" s="145"/>
-      <c r="I260" s="146"/>
+        <v>57</v>
+      </c>
+      <c r="H260" s="145">
+        <v>7892.5</v>
+      </c>
+      <c r="I260" s="146">
+        <v>7892.5</v>
+      </c>
       <c r="J260" s="147"/>
       <c r="K260" s="146"/>
-      <c r="L260" s="147"/>
-      <c r="M260" s="146"/>
+      <c r="L260" s="147">
+        <v>7892.5</v>
+      </c>
+      <c r="M260" s="146">
+        <v>7892.5</v>
+      </c>
       <c r="N260" s="147"/>
       <c r="O260" s="146"/>
       <c r="P260" s="147"/>
@@ -33309,9 +33362,7 @@
       <c r="W260" s="146"/>
       <c r="X260" s="147"/>
       <c r="Y260" s="146"/>
-      <c r="Z260" s="147">
-        <v>1870</v>
-      </c>
+      <c r="Z260" s="147"/>
       <c r="AA260" s="148"/>
       <c r="AB260" s="39"/>
       <c r="AC260" s="135"/>
@@ -33319,15 +33370,15 @@
       <c r="AE260" s="135"/>
       <c r="AF260" s="62">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1870</v>
+        <v>15785</v>
       </c>
       <c r="AG260" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
-        <v>0</v>
+        <v>15785</v>
       </c>
       <c r="AH260" s="63">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
-        <v>0</v>
+        <v>15785</v>
       </c>
       <c r="AI260" s="63">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -33347,7 +33398,7 @@
       </c>
       <c r="AM260" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="AN260" s="64">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -33355,15 +33406,15 @@
       </c>
       <c r="AO260" s="64">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
-        <v>0</v>
+        <v>15785</v>
       </c>
       <c r="AP260" s="64">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
-        <v>0</v>
+        <v>15785</v>
       </c>
       <c r="AQ260" s="64">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="AR260" s="64">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -33371,7 +33422,7 @@
       </c>
       <c r="AS260" s="14">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>15785</v>
       </c>
       <c r="AT260" s="88"/>
     </row>
@@ -33380,7 +33431,7 @@
         <v>146</v>
       </c>
       <c r="B261" s="65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C261" s="66" t="s">
         <v>47</v>
@@ -33415,17 +33466,17 @@
       <c r="W261" s="126"/>
       <c r="X261" s="125"/>
       <c r="Y261" s="126"/>
-      <c r="Z261" s="125">
-        <v>1945</v>
-      </c>
+      <c r="Z261" s="125"/>
       <c r="AA261" s="126"/>
-      <c r="AB261" s="125"/>
+      <c r="AB261" s="125">
+        <v>3000</v>
+      </c>
       <c r="AC261" s="126"/>
       <c r="AD261" s="125"/>
       <c r="AE261" s="126"/>
       <c r="AF261" s="63">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1945</v>
+        <v>3000</v>
       </c>
       <c r="AG261" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -33453,7 +33504,7 @@
       </c>
       <c r="AM261" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1945</v>
+        <v>3000</v>
       </c>
       <c r="AN261" s="63">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -33469,7 +33520,7 @@
       </c>
       <c r="AQ261" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1945</v>
+        <v>3000</v>
       </c>
       <c r="AR261" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -33486,7 +33537,7 @@
         <v>146</v>
       </c>
       <c r="B262" s="65" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C262" s="66" t="s">
         <v>47</v>
@@ -33521,17 +33572,17 @@
       <c r="W262" s="126"/>
       <c r="X262" s="125"/>
       <c r="Y262" s="126"/>
-      <c r="Z262" s="125">
-        <v>1620</v>
-      </c>
+      <c r="Z262" s="125"/>
       <c r="AA262" s="126"/>
-      <c r="AB262" s="125"/>
+      <c r="AB262" s="125">
+        <v>2434</v>
+      </c>
       <c r="AC262" s="126"/>
       <c r="AD262" s="125"/>
       <c r="AE262" s="126"/>
       <c r="AF262" s="63">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1620</v>
+        <v>2434</v>
       </c>
       <c r="AG262" s="63">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -33559,7 +33610,7 @@
       </c>
       <c r="AM262" s="63">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1620</v>
+        <v>2434</v>
       </c>
       <c r="AN262" s="63">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -33575,7 +33626,7 @@
       </c>
       <c r="AQ262" s="63">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1620</v>
+        <v>2434</v>
       </c>
       <c r="AR262" s="63">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -33592,10 +33643,10 @@
         <v>146</v>
       </c>
       <c r="B263" s="65" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C263" s="66" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D263" s="59" t="s">
         <v>148</v>
@@ -33607,7 +33658,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G263" s="69" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H263" s="125"/>
       <c r="I263" s="126"/>
@@ -33704,10 +33755,10 @@
         <v>146</v>
       </c>
       <c r="B264" s="65" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C264" s="59" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D264" s="59" t="s">
         <v>148</v>
@@ -33719,7 +33770,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G264" s="59" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H264" s="145"/>
       <c r="I264" s="146"/>
@@ -33816,7 +33867,7 @@
         <v>146</v>
       </c>
       <c r="B265" s="65" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C265" s="66" t="s">
         <v>73</v>
@@ -33851,11 +33902,11 @@
       <c r="W265" s="126"/>
       <c r="X265" s="125"/>
       <c r="Y265" s="126"/>
-      <c r="Z265" s="125">
+      <c r="Z265" s="125"/>
+      <c r="AA265" s="126"/>
+      <c r="AB265" s="125">
         <v>9647</v>
       </c>
-      <c r="AA265" s="126"/>
-      <c r="AB265" s="125"/>
       <c r="AC265" s="126"/>
       <c r="AD265" s="125"/>
       <c r="AE265" s="126"/>
@@ -33922,10 +33973,10 @@
         <v>146</v>
       </c>
       <c r="B266" s="65" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C266" s="59" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D266" s="59" t="s">
         <v>148</v>
@@ -33937,7 +33988,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G266" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H266" s="145"/>
       <c r="I266" s="146"/>
@@ -34030,7 +34081,7 @@
         <v>146</v>
       </c>
       <c r="B267" s="65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C267" s="59" t="s">
         <v>56</v>
@@ -34138,7 +34189,7 @@
         <v>146</v>
       </c>
       <c r="B268" s="65" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C268" s="66" t="s">
         <v>73</v>
@@ -34244,7 +34295,7 @@
         <v>146</v>
       </c>
       <c r="B269" s="65" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C269" s="66" t="s">
         <v>56</v>
@@ -34286,7 +34337,9 @@
       <c r="Z269" s="127">
         <v>28800</v>
       </c>
-      <c r="AA269" s="128"/>
+      <c r="AA269" s="128">
+        <v>14400</v>
+      </c>
       <c r="AB269" s="127"/>
       <c r="AC269" s="128"/>
       <c r="AD269" s="127"/>
@@ -34325,7 +34378,7 @@
       </c>
       <c r="AN269" s="176">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>14400</v>
       </c>
       <c r="AO269" s="176">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
@@ -34341,23 +34394,23 @@
       </c>
       <c r="AR269" s="176">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7200</v>
+        <v>21600</v>
       </c>
       <c r="AS269" s="129">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7200</v>
+        <v>21600</v>
       </c>
       <c r="AT269" s="88"/>
     </row>
     <row r="270" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A270" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B270" s="76" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C270" s="77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D270" s="77" t="s">
         <v>148</v>
@@ -34369,7 +34422,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G270" s="77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H270" s="125"/>
       <c r="I270" s="126"/>
@@ -34459,10 +34512,10 @@
     </row>
     <row r="271" spans="1:46" ht="24" x14ac:dyDescent="0.25">
       <c r="A271" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="B271" s="81" t="s">
         <v>198</v>
-      </c>
-      <c r="B271" s="81" t="s">
-        <v>200</v>
       </c>
       <c r="C271" s="77" t="s">
         <v>56</v>
@@ -34579,10 +34632,10 @@
     </row>
     <row r="272" spans="1:46" ht="24" x14ac:dyDescent="0.25">
       <c r="A272" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B272" s="81" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C272" s="77" t="s">
         <v>56</v>
@@ -34699,10 +34752,10 @@
     </row>
     <row r="273" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A273" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B273" s="76" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C273" s="77" t="s">
         <v>47</v>
@@ -34807,7 +34860,7 @@
     </row>
     <row r="274" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A274" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B274" s="76" t="s">
         <v>82</v>
@@ -34915,10 +34968,10 @@
     </row>
     <row r="275" spans="1:46" ht="30" x14ac:dyDescent="0.25">
       <c r="A275" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B275" s="76" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C275" s="77" t="s">
         <v>56</v>
@@ -35027,7 +35080,7 @@
     </row>
     <row r="276" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A276" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B276" s="89" t="s">
         <v>83</v>
@@ -35135,7 +35188,7 @@
     </row>
     <row r="277" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A277" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B277" s="76" t="s">
         <v>82</v>
@@ -35243,13 +35296,13 @@
     </row>
     <row r="278" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A278" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B278" s="76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C278" s="77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D278" s="77" t="s">
         <v>148</v>
@@ -35261,7 +35314,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G278" s="77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H278" s="125"/>
       <c r="I278" s="126"/>
@@ -35351,13 +35404,13 @@
     </row>
     <row r="279" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A279" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B279" s="76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C279" s="77" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D279" s="77" t="s">
         <v>148</v>
@@ -35369,7 +35422,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G279" s="77" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H279" s="125"/>
       <c r="I279" s="126"/>
@@ -35459,10 +35512,10 @@
     </row>
     <row r="280" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A280" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B280" s="89" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C280" s="77" t="s">
         <v>64</v>
@@ -35477,7 +35530,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G280" s="77" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H280" s="125"/>
       <c r="I280" s="126"/>
@@ -35567,13 +35620,13 @@
     </row>
     <row r="281" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A281" s="82" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B281" s="83" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C281" s="77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D281" s="84" t="s">
         <v>148</v>
@@ -35585,7 +35638,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G281" s="77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H281" s="139"/>
       <c r="I281" s="140"/>
@@ -35678,7 +35731,7 @@
     <dataValidation type="custom" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="C206" xr:uid="{79CEA303-1DCD-43F7-87CA-23C7083FD839}">
       <formula1>NOT(ISERROR(SEARCH(("Suministro"),(C206))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C56:C67 C114:C115 C147 C150:C151 C207:C213 C16:C17 C109:C110 C49 C204 C164:C172 C9 C51:C54 C153 C156:C158 C142 C19:C26" xr:uid="{903A75AC-B994-4CFA-A162-3C9C60CD0837}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C56:C67 C114:C115 C147 C150:C151 C207:C213 C16:C17 C109:C110 C49 C204 C164:C172 C9 C51:C54 C153 C156:C158 C142 C19:C26 C244" xr:uid="{903A75AC-B994-4CFA-A162-3C9C60CD0837}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0153BA12-49F1-46AB-BD37-EB57F3FE27FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1088DF65-DAB0-425D-8E1E-F8DD60B4FDA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34225,10 +34225,12 @@
       <c r="X268" s="125"/>
       <c r="Y268" s="126"/>
       <c r="Z268" s="125">
-        <v>14085</v>
+        <v>8350</v>
       </c>
       <c r="AA268" s="126"/>
-      <c r="AB268" s="125"/>
+      <c r="AB268" s="125">
+        <v>5735</v>
+      </c>
       <c r="AC268" s="126"/>
       <c r="AD268" s="125"/>
       <c r="AE268" s="126"/>
